--- a/worklists/grapes_updates_to_enter.xlsx
+++ b/worklists/grapes_updates_to_enter.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record 1049" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Updates'!$A$1:$M$206</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Check'!$A$1:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Updates'!$A$1:$N$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Check'!$A$1:$J$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Review for removal'!$A$1:$E$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -705,12 +705,19 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Some new deadlines have already passed: the sponsor hadn't posted the next cycle in September. Enter the newer date,</t>
+          <t>Award amount is what the sponsor page said in September. "Not listed" means it wasn't found; check the sponsor page.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Some new deadlines have already passed: the sponsor hadn't posted the next cycle in September. Enter the newer date,</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>but check the page first in case the next cycle is now posted.</t>
         </is>
@@ -727,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M206"/>
+  <dimension ref="A1:N206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -740,9 +747,10 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -796,17 +804,22 @@
           <t>New website (grey = unchanged, link only)</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Award amount</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Backend shows</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -845,9 +858,14 @@
           <t>www.cfa.harvard.edu/opportunities/fellowships-visiting-scientist-positions/cfa-fellowship</t>
         </is>
       </c>
-      <c r="K2" s="11" t="n"/>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L2" s="11" t="n"/>
-      <c r="M2" s="12" t="n"/>
+      <c r="M2" s="11" t="n"/>
+      <c r="N2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -882,9 +900,14 @@
           <t>www.cfa.harvard.edu/opportunities/fellowships-visiting-scientist-positions/clay-fellowship</t>
         </is>
       </c>
-      <c r="K3" s="11" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L3" s="11" t="n"/>
-      <c r="M3" s="12" t="n"/>
+      <c r="M3" s="11" t="n"/>
+      <c r="N3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -919,9 +942,14 @@
           <t>www.americanantiquarian.org/12-month-residential/hench-post-dissertation-fellowship</t>
         </is>
       </c>
-      <c r="K4" s="11" t="n"/>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>$44,000</t>
+        </is>
+      </c>
       <c r="L4" s="11" t="n"/>
-      <c r="M4" s="12" t="n"/>
+      <c r="M4" s="11" t="n"/>
+      <c r="N4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -954,9 +982,14 @@
           <t>societyhumanities.as.cornell.edu/mellon-postdoctoral-fellowships</t>
         </is>
       </c>
-      <c r="K5" s="11" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>$64,000 per year</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -991,9 +1024,14 @@
           <t>fellowships.si.edu/opportunity/smithsonian-institution-fellowship-program-sifp</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>$10,000-$57,000 annually</t>
+        </is>
+      </c>
       <c r="L6" s="11" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -1028,9 +1066,14 @@
           <t>www.nsf.gov/funding/opportunities/grfp-nsf-graduate-research-fellowship-program</t>
         </is>
       </c>
-      <c r="K7" s="11" t="n"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>$37,000 annual stipend plus $16,000 annual cost of education allowance for three years within five-year fellowship</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1065,9 +1108,14 @@
           <t>atkinson.cornell.edu/grants/postdocs/postdoctoral-fellowships</t>
         </is>
       </c>
-      <c r="K8" s="11" t="n"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Stipend (amount not specified); professional development support</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -1102,9 +1150,14 @@
           <t>asp.ucar.edu/postdocs/postdoctoral-fellowships</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Competitive salary + benefits for 2 years</t>
+        </is>
+      </c>
       <c r="L9" s="11" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -1137,9 +1190,14 @@
           <t>apsanet.org/diversity/diversity-fellowship-program</t>
         </is>
       </c>
-      <c r="K10" s="11" t="n"/>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>$2,000-$5,000</t>
+        </is>
+      </c>
       <c r="L10" s="11" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1174,9 +1232,14 @@
           <t>www.hhmi.org/programs/gilliam-fellows</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>$53,000/year (including $36,000 stipend + $10,000 institutional allowance + $4,000 discretionary + $3,000 community engagement)</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1211,9 +1274,14 @@
           <t>www.nsf.gov/funding/opportunities/ear-pf-earth-sciences-postdoctoral-fellowships</t>
         </is>
       </c>
-      <c r="K12" s="11" t="n"/>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1248,9 +1316,14 @@
           <t>www.acls.org/competitions/luce-acls-dissertation-fellowships-in-american-art</t>
         </is>
       </c>
-      <c r="K13" s="11" t="n"/>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>$42,500 ($38,000 stipend + $4,500 travel/research allowance)</t>
+        </is>
+      </c>
       <c r="L13" s="11" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1285,9 +1358,14 @@
           <t>pdsoros.org</t>
         </is>
       </c>
-      <c r="K14" s="11" t="n"/>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Up to $90,000 over two years ($40,000 tuition + $50,000 stipend)</t>
+        </is>
+      </c>
       <c r="L14" s="11" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1322,9 +1400,14 @@
           <t>www.hertzfoundation.org/hertz-fellowship</t>
         </is>
       </c>
-      <c r="K15" s="11" t="n"/>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Up to $250,000 over 5 years</t>
+        </is>
+      </c>
       <c r="L15" s="11" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1359,9 +1442,14 @@
           <t>www2.daad.de/deutschland/stipendium/datenbank/en/21148-scholarship-database/?detail=50026200</t>
         </is>
       </c>
-      <c r="K16" s="11" t="n"/>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>€992-€1,300 monthly (varies by program) plus travel allowance and insurance</t>
+        </is>
+      </c>
       <c r="L16" s="11" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1396,9 +1484,14 @@
           <t>ndseg.org</t>
         </is>
       </c>
-      <c r="K17" s="11" t="n"/>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>$40,800 annual stipend; covers full tuition and mandatory fees over three years plus travel and health insurance budgets</t>
+        </is>
+      </c>
       <c r="L17" s="11" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1433,9 +1526,14 @@
           <t>www.phrmafoundation.org/grants-fellowships/postdoctoral-fellowships</t>
         </is>
       </c>
-      <c r="K18" s="11" t="n"/>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>$60,000 per year for up to 2 years</t>
+        </is>
+      </c>
       <c r="L18" s="11" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1470,9 +1568,14 @@
           <t>www.climate.columbia.edu/postdoctoral-research-program</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n"/>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>$72,116/year plus $12,000 research stipend</t>
+        </is>
+      </c>
       <c r="L19" s="11" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -1507,9 +1610,14 @@
           <t>www.daad.org/en/find-funding/scholarship-database</t>
         </is>
       </c>
-      <c r="K20" s="11" t="n"/>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L20" s="11" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1542,9 +1650,14 @@
           <t>www.acifoundation.org/scholarships.aspx</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>$10,000 stipend plus convention travel</t>
+        </is>
+      </c>
       <c r="L21" s="11" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1579,9 +1692,14 @@
           <t>diversity.berkeley.edu/programs-services/postdoctoral-diversity</t>
         </is>
       </c>
-      <c r="K22" s="11" t="n"/>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L22" s="11" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1616,9 +1734,14 @@
           <t>newcombefoundation.org/fellowships</t>
         </is>
       </c>
-      <c r="K23" s="11" t="n"/>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>$31,000 stipend for final year of dissertation writing</t>
+        </is>
+      </c>
       <c r="L23" s="11" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -1653,9 +1776,14 @@
           <t>www.lbi.org/about/fellowships/lbi-daad-fellowships</t>
         </is>
       </c>
-      <c r="K24" s="11" t="n"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L24" s="11" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1692,9 +1820,14 @@
           <t>www.nationalacademies.org/programs/PGA-FP-18-P-23</t>
         </is>
       </c>
-      <c r="K25" s="11" t="n"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Competitive postdoctoral stipend (varies)</t>
+        </is>
+      </c>
       <c r="L25" s="11" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1729,9 +1862,14 @@
           <t>npp.orau.org</t>
         </is>
       </c>
-      <c r="K26" s="11" t="n"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Includes health insurance, research allowance ($10,000/year), professional development, relocation reimbursement</t>
+        </is>
+      </c>
       <c r="L26" s="11" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="M26" s="11" t="n"/>
+      <c r="N26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1766,9 +1904,14 @@
           <t>www.aarome.org/apply/rome-prize</t>
         </is>
       </c>
-      <c r="K27" s="11" t="n"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Stipend, bedroom with private bath, and private workspace provided</t>
+        </is>
+      </c>
       <c r="L27" s="11" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -1803,9 +1946,14 @@
           <t>www.acls.org/competitions/luce-acls-early-career-fellowships-in-china-studies-flexible</t>
         </is>
       </c>
-      <c r="K28" s="11" t="n"/>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>$15,000 - $45,000</t>
+        </is>
+      </c>
       <c r="L28" s="11" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1840,9 +1988,14 @@
           <t>apgianninifoundation.org</t>
         </is>
       </c>
-      <c r="K29" s="11" t="n"/>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>$70,000/year for three years</t>
+        </is>
+      </c>
       <c r="L29" s="11" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1875,9 +2028,14 @@
           <t>www.postdocs.ubc.ca/award/killam-postdoctoral-research-fellowship</t>
         </is>
       </c>
-      <c r="K30" s="11" t="n"/>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>$60,000 annually</t>
+        </is>
+      </c>
       <c r="L30" s="11" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1916,9 +2074,14 @@
           <t>www.csus.edu/center/center-california-studies/capital-fellows</t>
         </is>
       </c>
-      <c r="K31" s="11" t="n"/>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>~$3,000/month stipend for 11 months</t>
+        </is>
+      </c>
       <c r="L31" s="11" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -1953,9 +2116,14 @@
           <t>www.asianculturalcouncil.org/grant-opportunities</t>
         </is>
       </c>
-      <c r="K32" s="11" t="n"/>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Varies by program</t>
+        </is>
+      </c>
       <c r="L32" s="11" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1990,9 +2158,14 @@
           <t>www.assembly.ca.gov/california-state-assembly-fellowship-program</t>
         </is>
       </c>
-      <c r="K33" s="11" t="n"/>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L33" s="11" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -2031,9 +2204,14 @@
           <t>www.csus.edu/center/center-california-studies/capital-fellows</t>
         </is>
       </c>
-      <c r="K34" s="11" t="n"/>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>~$3,000/month stipend for 11 months</t>
+        </is>
+      </c>
       <c r="L34" s="11" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="M34" s="11" t="n"/>
+      <c r="N34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -2068,9 +2246,14 @@
           <t>dowjonesnewsfund.org/djnfinternships</t>
         </is>
       </c>
-      <c r="K35" s="11" t="n"/>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>$1,500 scholarship plus paid internship</t>
+        </is>
+      </c>
       <c r="L35" s="11" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="M35" s="11" t="n"/>
+      <c r="N35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -2105,9 +2288,14 @@
           <t>jetprogramme.org</t>
         </is>
       </c>
-      <c r="K36" s="11" t="n"/>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Full-time employment salary + benefits</t>
+        </is>
+      </c>
       <c r="L36" s="11" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -2144,9 +2332,14 @@
           <t>internships.si.edu/opportunity/internships-national-museum-american-indian</t>
         </is>
       </c>
-      <c r="K37" s="11" t="n"/>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>Varies by position</t>
+        </is>
+      </c>
       <c r="L37" s="11" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="M37" s="11" t="n"/>
+      <c r="N37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -2181,9 +2374,14 @@
           <t>www.supremecourt.gov/fellows</t>
         </is>
       </c>
-      <c r="K38" s="11" t="n"/>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>$120,579 (equivalent to GS-13/1 federal salary)</t>
+        </is>
+      </c>
       <c r="L38" s="11" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="M38" s="11" t="n"/>
+      <c r="N38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -2222,9 +2420,14 @@
           <t>grants.nih.gov/grants/guide/pa-files/PAR-24-052.html</t>
         </is>
       </c>
-      <c r="K39" s="11" t="n"/>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>$42,500 salary/year + $28,656 additional expenses</t>
+        </is>
+      </c>
       <c r="L39" s="11" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -2259,9 +2462,14 @@
           <t>www.indiastudies.org/research-fellowship-programs</t>
         </is>
       </c>
-      <c r="K40" s="11" t="n"/>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>$7,000 (Junior); varies for Senior</t>
+        </is>
+      </c>
       <c r="L40" s="11" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -2296,9 +2504,14 @@
           <t>www.leifureirikssonfoundation.org</t>
         </is>
       </c>
-      <c r="K41" s="11" t="n"/>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>Up to $25,000 including travel</t>
+        </is>
+      </c>
       <c r="L41" s="11" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="M41" s="11" t="n"/>
+      <c r="N41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -2337,9 +2550,14 @@
           <t>www.onr.navy.mil/education-outreach/undergraduate-graduate/nreip-naval-internship</t>
         </is>
       </c>
-      <c r="K42" s="11" t="n"/>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>Paid internship (salary varies)</t>
+        </is>
+      </c>
       <c r="L42" s="11" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -2378,9 +2596,14 @@
           <t>khmerstudies.org/programs/us-scholar-research-fellowships</t>
         </is>
       </c>
-      <c r="K43" s="11" t="n"/>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Up to 11 months; stipend based on project and duration</t>
+        </is>
+      </c>
       <c r="L43" s="11" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="M43" s="11" t="n"/>
+      <c r="N43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -2415,9 +2638,14 @@
           <t>www.cancer.org/research/we-fund-cancer-research/apply-research-grant/grant-types/postdoctoral-fellowships.html</t>
         </is>
       </c>
-      <c r="K44" s="11" t="n"/>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>$66,000-$70,000/year</t>
+        </is>
+      </c>
       <c r="L44" s="11" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="M44" s="11" t="n"/>
+      <c r="N44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -2452,9 +2680,14 @@
           <t>www.lung.org/research/awards-and-grants-opportunities</t>
         </is>
       </c>
-      <c r="K45" s="11" t="n"/>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>$21,000/year (Lung Health Dissertation Grant)</t>
+        </is>
+      </c>
       <c r="L45" s="11" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="M45" s="11" t="n"/>
+      <c r="N45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -2489,9 +2722,14 @@
           <t>eit.org/education-and-scholarships/graduate</t>
         </is>
       </c>
-      <c r="K46" s="11" t="n"/>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L46" s="11" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="M46" s="11" t="n"/>
+      <c r="N46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -2526,9 +2764,14 @@
           <t>ny.jpf.go.jp/grants/grants-for-japanese-studies/fellowship-program</t>
         </is>
       </c>
-      <c r="K47" s="11" t="n"/>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L47" s="11" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="M47" s="11" t="n"/>
+      <c r="N47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -2563,9 +2806,14 @@
           <t>www.newberry.org/research/fellowships/short-term-fellowships</t>
         </is>
       </c>
-      <c r="K48" s="11" t="n"/>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>$3,000/month</t>
+        </is>
+      </c>
       <c r="L48" s="11" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="M48" s="11" t="n"/>
+      <c r="N48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -2600,9 +2848,14 @@
           <t>aiar.org/fellowships</t>
         </is>
       </c>
-      <c r="K49" s="11" t="n"/>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>$3,000–$20,000 depending on fellowship type</t>
+        </is>
+      </c>
       <c r="L49" s="11" t="n"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="M49" s="11" t="n"/>
+      <c r="N49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -2637,9 +2890,14 @@
           <t>iac.ucla.edu/funding/graduate</t>
         </is>
       </c>
-      <c r="K50" s="11" t="n"/>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Tuition + $6,000-$7,400/quarter</t>
+        </is>
+      </c>
       <c r="L50" s="11" t="n"/>
-      <c r="M50" s="12" t="n"/>
+      <c r="M50" s="11" t="n"/>
+      <c r="N50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -2672,9 +2930,14 @@
           <t>grants.nih.gov/funding/activity-codes/F31</t>
         </is>
       </c>
-      <c r="K51" s="11" t="n"/>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Stipend, tuition/fees, institutional allowance</t>
+        </is>
+      </c>
       <c r="L51" s="11" t="n"/>
-      <c r="M51" s="12" t="n"/>
+      <c r="M51" s="11" t="n"/>
+      <c r="N51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -2713,9 +2976,14 @@
           <t>grants.nih.gov/grants/guide/pa-files/PA-25-422.html</t>
         </is>
       </c>
-      <c r="K52" s="11" t="n"/>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>NIH stipend rates + tuition/fees contribution + institutional allowance</t>
+        </is>
+      </c>
       <c r="L52" s="11" t="n"/>
-      <c r="M52" s="12" t="n"/>
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -2750,9 +3018,14 @@
           <t>www.switzernetwork.org/fellowship/become-fellow</t>
         </is>
       </c>
-      <c r="K53" s="11" t="n"/>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L53" s="11" t="n"/>
-      <c r="M53" s="12" t="n"/>
+      <c r="M53" s="11" t="n"/>
+      <c r="N53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -2787,9 +3060,14 @@
           <t>www.ets.org/toefl/grants/doctoral-research-grant-language-assessment.html</t>
         </is>
       </c>
-      <c r="K54" s="11" t="n"/>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>Up to $3,000 per award (up to 5 awards annually)</t>
+        </is>
+      </c>
       <c r="L54" s="11" t="n"/>
-      <c r="M54" s="12" t="n"/>
+      <c r="M54" s="11" t="n"/>
+      <c r="N54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2824,9 +3102,14 @@
           <t>www.apaics.org/congressional-fellowship</t>
         </is>
       </c>
-      <c r="K55" s="11" t="n"/>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>$3,700/month educational stipend plus living stipend and health insurance</t>
+        </is>
+      </c>
       <c r="L55" s="11" t="n"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="M55" s="11" t="n"/>
+      <c r="N55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -2861,9 +3144,14 @@
           <t>airandspace.si.edu/get-involved/fellowships/guggenheim</t>
         </is>
       </c>
-      <c r="K56" s="11" t="n"/>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>$40,000-$55,000 per year</t>
+        </is>
+      </c>
       <c r="L56" s="11" t="n"/>
-      <c r="M56" s="12" t="n"/>
+      <c r="M56" s="11" t="n"/>
+      <c r="N56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2898,9 +3186,14 @@
           <t>rijs.fas.harvard.edu/postdoctoral/rijs</t>
         </is>
       </c>
-      <c r="K57" s="11" t="n"/>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>$70,000 stipend plus $5,000 research funds</t>
+        </is>
+      </c>
       <c r="L57" s="11" t="n"/>
-      <c r="M57" s="12" t="n"/>
+      <c r="M57" s="11" t="n"/>
+      <c r="N57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -2935,9 +3228,14 @@
           <t>business.edf.org/climate-corps/fellows/us</t>
         </is>
       </c>
-      <c r="K58" s="11" t="n"/>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>$1,400+/week + $1,400 Foundations Week</t>
+        </is>
+      </c>
       <c r="L58" s="11" t="n"/>
-      <c r="M58" s="12" t="n"/>
+      <c r="M58" s="11" t="n"/>
+      <c r="N58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2976,9 +3274,14 @@
           <t>www.mountvernon.org/library/fellowships/fellows-program</t>
         </is>
       </c>
-      <c r="K59" s="11" t="n"/>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>Stipend + on-site housing; length and amount vary by fellowship type</t>
+        </is>
+      </c>
       <c r="L59" s="11" t="n"/>
-      <c r="M59" s="12" t="n"/>
+      <c r="M59" s="11" t="n"/>
+      <c r="N59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -3013,9 +3316,14 @@
           <t>cushwa.nd.edu/grant-opportunities/research-travel-grants</t>
         </is>
       </c>
-      <c r="K60" s="11" t="n"/>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>Up to $2,000</t>
+        </is>
+      </c>
       <c r="L60" s="11" t="n"/>
-      <c r="M60" s="12" t="n"/>
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -3050,9 +3358,14 @@
           <t>www.cc.nih.gov/bioethics/education</t>
         </is>
       </c>
-      <c r="K61" s="11" t="n"/>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Fully funded</t>
+        </is>
+      </c>
       <c r="L61" s="11" t="n"/>
-      <c r="M61" s="12" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -3087,9 +3400,14 @@
           <t>www.aaas.org/programs/mass-media-fellowship</t>
         </is>
       </c>
-      <c r="K62" s="11" t="n"/>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Approximately $9,000 for summer internship</t>
+        </is>
+      </c>
       <c r="L62" s="11" t="n"/>
-      <c r="M62" s="12" t="n"/>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -3124,9 +3442,14 @@
           <t>www.ncaa.org/sports/2013/11/21/walter-byers-graduate-scholarship.aspx</t>
         </is>
       </c>
-      <c r="K63" s="11" t="n"/>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>$24,000 (renewable for second year)</t>
+        </is>
+      </c>
       <c r="L63" s="11" t="n"/>
-      <c r="M63" s="12" t="n"/>
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -3161,9 +3484,14 @@
           <t>www.krellinst.org/csgf</t>
         </is>
       </c>
-      <c r="K64" s="11" t="n"/>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>$38,000 annual stipend plus full tuition coverage</t>
+        </is>
+      </c>
       <c r="L64" s="11" t="n"/>
-      <c r="M64" s="12" t="n"/>
+      <c r="M64" s="11" t="n"/>
+      <c r="N64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -3198,9 +3526,14 @@
           <t>leakeyfoundation.org/grant/research</t>
         </is>
       </c>
-      <c r="K65" s="11" t="n"/>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>$3,000-$20,000 for doctoral students; up to $30,000 for post-PhD</t>
+        </is>
+      </c>
       <c r="L65" s="11" t="n"/>
-      <c r="M65" s="12" t="n"/>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -3235,9 +3568,14 @@
           <t>www.americanantiquarian.org/short-term-fellowships</t>
         </is>
       </c>
-      <c r="K66" s="11" t="n"/>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Varies by specific fellowship (covers room and board)</t>
+        </is>
+      </c>
       <c r="L66" s="11" t="n"/>
-      <c r="M66" s="12" t="n"/>
+      <c r="M66" s="11" t="n"/>
+      <c r="N66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -3272,9 +3610,14 @@
           <t>librarycompany.org/academic-programs/fellowships-2-2/short-term</t>
         </is>
       </c>
-      <c r="K67" s="11" t="n"/>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>$3,000 per month</t>
+        </is>
+      </c>
       <c r="L67" s="11" t="n"/>
-      <c r="M67" s="12" t="n"/>
+      <c r="M67" s="11" t="n"/>
+      <c r="N67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -3309,9 +3652,14 @@
           <t>www.borenawards.org</t>
         </is>
       </c>
-      <c r="K68" s="11" t="n"/>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>Up to $30,000</t>
+        </is>
+      </c>
       <c r="L68" s="11" t="n"/>
-      <c r="M68" s="12" t="n"/>
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -3346,9 +3694,14 @@
           <t>stemfellowships.org</t>
         </is>
       </c>
-      <c r="K69" s="11" t="n"/>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>$20,000 annually, renewable for 3–6 years</t>
+        </is>
+      </c>
       <c r="L69" s="11" t="n"/>
-      <c r="M69" s="12" t="n"/>
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -3383,9 +3736,14 @@
           <t>www.pbk.org/awards/sibley-fellowship</t>
         </is>
       </c>
-      <c r="K70" s="11" t="n"/>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>$20,000</t>
+        </is>
+      </c>
       <c r="L70" s="11" t="n"/>
-      <c r="M70" s="12" t="n"/>
+      <c r="M70" s="11" t="n"/>
+      <c r="N70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -3420,9 +3778,14 @@
           <t>nwtrustee.com/alfred-g-and-elma-m-milotte-scholarship</t>
         </is>
       </c>
-      <c r="K71" s="11" t="n"/>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>$4,000</t>
+        </is>
+      </c>
       <c r="L71" s="11" t="n"/>
-      <c r="M71" s="12" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -3457,9 +3820,14 @@
           <t>www.1718.ucla.edu/research/fellowships</t>
         </is>
       </c>
-      <c r="K72" s="11" t="n"/>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L72" s="11" t="n"/>
-      <c r="M72" s="12" t="n"/>
+      <c r="M72" s="11" t="n"/>
+      <c r="N72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -3494,9 +3862,14 @@
           <t>www.fraxa.org/fragile-x-research/grant-application</t>
         </is>
       </c>
-      <c r="K73" s="11" t="n"/>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>$50,000 per year for up to 2 years</t>
+        </is>
+      </c>
       <c r="L73" s="11" t="n"/>
-      <c r="M73" s="12" t="n"/>
+      <c r="M73" s="11" t="n"/>
+      <c r="N73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -3531,9 +3904,14 @@
           <t>www.hfg.org/programs</t>
         </is>
       </c>
-      <c r="K74" s="11" t="n"/>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>$25,000 for one year</t>
+        </is>
+      </c>
       <c r="L74" s="11" t="n"/>
-      <c r="M74" s="12" t="n"/>
+      <c r="M74" s="11" t="n"/>
+      <c r="N74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -3568,9 +3946,14 @@
           <t>www.jccfund.org</t>
         </is>
       </c>
-      <c r="K75" s="11" t="n"/>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>Three-year postdoctoral salary support</t>
+        </is>
+      </c>
       <c r="L75" s="11" t="n"/>
-      <c r="M75" s="12" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -3605,9 +3988,14 @@
           <t>www.1718.ucla.edu/research/kanner</t>
         </is>
       </c>
-      <c r="K76" s="11" t="n"/>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>$69,073 for three consecutive quarters in residence</t>
+        </is>
+      </c>
       <c r="L76" s="11" t="n"/>
-      <c r="M76" s="12" t="n"/>
+      <c r="M76" s="11" t="n"/>
+      <c r="N76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -3642,9 +4030,14 @@
           <t>www.asianstudies.org/grants-awards/council-grants/northeast-asia-council-korean-studies-grants</t>
         </is>
       </c>
-      <c r="K77" s="11" t="n"/>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Up to $5,000</t>
+        </is>
+      </c>
       <c r="L77" s="11" t="n"/>
-      <c r="M77" s="12" t="n"/>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -3679,9 +4072,14 @@
           <t>www.jeffersonscholars.org/fellowships/national</t>
         </is>
       </c>
-      <c r="K78" s="11" t="n"/>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>$30,000/year</t>
+        </is>
+      </c>
       <c r="L78" s="11" t="n"/>
-      <c r="M78" s="12" t="n"/>
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -3714,9 +4112,14 @@
           <t>cleancompetition.org/programs/fellowship-program</t>
         </is>
       </c>
-      <c r="K79" s="11" t="n"/>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>$60,000 annually for 2 years (up to $37,500 year 3)</t>
+        </is>
+      </c>
       <c r="L79" s="11" t="n"/>
-      <c r="M79" s="12" t="n"/>
+      <c r="M79" s="11" t="n"/>
+      <c r="N79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -3751,9 +4154,14 @@
           <t>iac.ucla.edu/funding/grants</t>
         </is>
       </c>
-      <c r="K80" s="11" t="n"/>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>$7,000-$10,000</t>
+        </is>
+      </c>
       <c r="L80" s="11" t="n"/>
-      <c r="M80" s="12" t="n"/>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -3788,9 +4196,14 @@
           <t>www.1718.ucla.edu/research/wilde-holland-fellowship</t>
         </is>
       </c>
-      <c r="K81" s="11" t="n"/>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>$4,000/month</t>
+        </is>
+      </c>
       <c r="L81" s="11" t="n"/>
-      <c r="M81" s="12" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -3823,9 +4236,14 @@
           <t>www.mbari.org/about/careers/internships</t>
         </is>
       </c>
-      <c r="K82" s="11" t="n"/>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>$23/hour + shared housing</t>
+        </is>
+      </c>
       <c r="L82" s="11" t="n"/>
-      <c r="M82" s="12" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -3860,9 +4278,14 @@
           <t>www.ashrae.org/communities/student-zone/scholarships-and-grants/graduate-student-grant-in-aid-award-program</t>
         </is>
       </c>
-      <c r="K83" s="11" t="n"/>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>$7,500</t>
+        </is>
+      </c>
       <c r="L83" s="11" t="n"/>
-      <c r="M83" s="12" t="n"/>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -3897,9 +4320,14 @@
           <t>hooverpresidentialfoundation.org/research-travel-grant</t>
         </is>
       </c>
-      <c r="K84" s="11" t="n"/>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>$500-$2,000</t>
+        </is>
+      </c>
       <c r="L84" s="11" t="n"/>
-      <c r="M84" s="12" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -3934,9 +4362,14 @@
           <t>www.amphilsoc.org/grants/fellowships</t>
         </is>
       </c>
-      <c r="K85" s="11" t="n"/>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>$3,000/month</t>
+        </is>
+      </c>
       <c r="L85" s="11" t="n"/>
-      <c r="M85" s="12" t="n"/>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -3971,9 +4404,14 @@
           <t>www.amphilsoc.org/grants/phillips-fund-native-american-research</t>
         </is>
       </c>
-      <c r="K86" s="11" t="n"/>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>Average grant ~$3,000 (up to $3,500)</t>
+        </is>
+      </c>
       <c r="L86" s="11" t="n"/>
-      <c r="M86" s="12" t="n"/>
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -4006,9 +4444,14 @@
           <t>www.doaks.org/research/fellowships-and-awards/bliss-symposium-awards</t>
         </is>
       </c>
-      <c r="K87" s="11" t="n"/>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>$1,000–$1,500 travel reimbursement; symposium registration waived</t>
+        </is>
+      </c>
       <c r="L87" s="11" t="n"/>
-      <c r="M87" s="12" t="n"/>
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -4043,9 +4486,14 @@
           <t>capitolhistory.org/engage/capitol-fellowship</t>
         </is>
       </c>
-      <c r="K88" s="11" t="n"/>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>$2,500/month</t>
+        </is>
+      </c>
       <c r="L88" s="11" t="n"/>
-      <c r="M88" s="12" t="n"/>
+      <c r="M88" s="11" t="n"/>
+      <c r="N88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -4080,9 +4528,14 @@
           <t>wennergren.org/program/post-phd-research-grant</t>
         </is>
       </c>
-      <c r="K89" s="11" t="n"/>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Up to $25,000</t>
+        </is>
+      </c>
       <c r="L89" s="11" t="n"/>
-      <c r="M89" s="12" t="n"/>
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -4117,9 +4570,14 @@
           <t>www2.whoi.edu/site/nosams/opportunities/graduate-student-internship-program</t>
         </is>
       </c>
-      <c r="K90" s="11" t="n"/>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>Analytical costs, travel, accommodation, and subsistence covered</t>
+        </is>
+      </c>
       <c r="L90" s="11" t="n"/>
-      <c r="M90" s="12" t="n"/>
+      <c r="M90" s="11" t="n"/>
+      <c r="N90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -4162,9 +4620,14 @@
           <t>www.st-annes.ox.ac.uk/wp-content/uploads/2025/01/Biegun-Warburg-JRF-25-27-FPs.pdf</t>
         </is>
       </c>
-      <c r="K91" s="11" t="n"/>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L91" s="11" t="n"/>
-      <c r="M91" s="12" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -4201,9 +4664,14 @@
           <t>leakeyfoundation.org/grant/baldwin</t>
         </is>
       </c>
-      <c r="K92" s="11" t="n"/>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>Up to $15,000/year for up to two years</t>
+        </is>
+      </c>
       <c r="L92" s="11" t="n"/>
-      <c r="M92" s="12" t="n"/>
+      <c r="M92" s="11" t="n"/>
+      <c r="N92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -4242,9 +4710,14 @@
           <t>seg.org/programs/student-programs/scholarships</t>
         </is>
       </c>
-      <c r="K93" s="11" t="n"/>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>$500 - $10,000 per year</t>
+        </is>
+      </c>
       <c r="L93" s="11" t="n"/>
-      <c r="M93" s="12" t="n"/>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -4283,9 +4756,14 @@
           <t>nature.berkeley.edu/academics/ciriacy-wantrup</t>
         </is>
       </c>
-      <c r="K94" s="11" t="n"/>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>$69,073–$77,030 annually</t>
+        </is>
+      </c>
       <c r="L94" s="11" t="n"/>
-      <c r="M94" s="12" t="n"/>
+      <c r="M94" s="11" t="n"/>
+      <c r="N94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -4324,9 +4802,14 @@
           <t>www.linkenergy.org</t>
         </is>
       </c>
-      <c r="K95" s="11" t="n"/>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>$35,000/year for two years ($70,000 total)</t>
+        </is>
+      </c>
       <c r="L95" s="11" t="n"/>
-      <c r="M95" s="12" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -4365,9 +4848,14 @@
           <t>us-japan.wcfia.harvard.edu/apply-become-postdoctoral-fellow</t>
         </is>
       </c>
-      <c r="K96" s="11" t="n"/>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>Year-long stipend (commencing August or September 2026)</t>
+        </is>
+      </c>
       <c r="L96" s="11" t="n"/>
-      <c r="M96" s="12" t="n"/>
+      <c r="M96" s="11" t="n"/>
+      <c r="N96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -4406,9 +4894,14 @@
           <t>research.ibm.com/goldstine</t>
         </is>
       </c>
-      <c r="K97" s="11" t="n"/>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>Competitive postdoctoral salary and benefits</t>
+        </is>
+      </c>
       <c r="L97" s="11" t="n"/>
-      <c r="M97" s="12" t="n"/>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -4447,9 +4940,14 @@
           <t>www.ntu.edu.sg/research/research-careers/presidential-postdoctoral-fellowship-(ppf)</t>
         </is>
       </c>
-      <c r="K98" s="11" t="n"/>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>SGD 80,000/year (~USD 60,000) + research support</t>
+        </is>
+      </c>
       <c r="L98" s="11" t="n"/>
-      <c r="M98" s="12" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -4492,9 +4990,14 @@
           <t>www.ualberta.ca/en/graduate-studies/awards-and-funding/postdoctoral-fellow-funding/killam.html</t>
         </is>
       </c>
-      <c r="K99" s="11" t="n"/>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>$4,000 research allowance</t>
+        </is>
+      </c>
       <c r="L99" s="11" t="n"/>
-      <c r="M99" s="12" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -4537,9 +5040,14 @@
           <t>www.ualberta.ca/en/graduate-studies/awards-and-funding/postdoctoral-fellow-funding/killam.html</t>
         </is>
       </c>
-      <c r="K100" s="11" t="n"/>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>$50,000/year + benefits + $4,000 one-time research/travel grant</t>
+        </is>
+      </c>
       <c r="L100" s="11" t="n"/>
-      <c r="M100" s="12" t="n"/>
+      <c r="M100" s="11" t="n"/>
+      <c r="N100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -4578,9 +5086,14 @@
           <t>www.nyhistory.org/careers/fellowships</t>
         </is>
       </c>
-      <c r="K101" s="11" t="n"/>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>$60,000 stipend + benefits for 10 months</t>
+        </is>
+      </c>
       <c r="L101" s="11" t="n"/>
-      <c r="M101" s="12" t="n"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -4619,9 +5132,14 @@
           <t>www.nyhistory.org/careers/fellowships</t>
         </is>
       </c>
-      <c r="K102" s="11" t="n"/>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>$20,000 stipend for 10 months</t>
+        </is>
+      </c>
       <c r="L102" s="11" t="n"/>
-      <c r="M102" s="12" t="n"/>
+      <c r="M102" s="11" t="n"/>
+      <c r="N102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -4660,9 +5178,14 @@
           <t>fairbank.fas.harvard.edu/affiliation-2/an-wang-postdoctoral-fellows</t>
         </is>
       </c>
-      <c r="K103" s="11" t="n"/>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>$67,600 annual stipend</t>
+        </is>
+      </c>
       <c r="L103" s="11" t="n"/>
-      <c r="M103" s="12" t="n"/>
+      <c r="M103" s="11" t="n"/>
+      <c r="N103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -4701,9 +5224,14 @@
           <t>www.winterthur.org/fellowships-available</t>
         </is>
       </c>
-      <c r="K104" s="11" t="n"/>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>Varies by fellowship length (covers room and board for residential)</t>
+        </is>
+      </c>
       <c r="L104" s="11" t="n"/>
-      <c r="M104" s="12" t="n"/>
+      <c r="M104" s="11" t="n"/>
+      <c r="N104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -4744,9 +5272,14 @@
           <t>pasadenacf.org/programs/scholarships/josephine-de-karman-trust-fellowship</t>
         </is>
       </c>
-      <c r="K105" s="11" t="n"/>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>$28,000</t>
+        </is>
+      </c>
       <c r="L105" s="11" t="n"/>
-      <c r="M105" s="12" t="n"/>
+      <c r="M105" s="11" t="n"/>
+      <c r="N105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -4787,9 +5320,14 @@
           <t>www.ans.org/scholarships</t>
         </is>
       </c>
-      <c r="K106" s="11" t="n"/>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>$1,000–$5,000 depending on scholarship</t>
+        </is>
+      </c>
       <c r="L106" s="11" t="n"/>
-      <c r="M106" s="12" t="n"/>
+      <c r="M106" s="11" t="n"/>
+      <c r="N106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -4832,9 +5370,14 @@
           <t>1718.ucla.edu/research/fellowships</t>
         </is>
       </c>
-      <c r="K107" s="11" t="n"/>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>$12,000 for 3 months</t>
+        </is>
+      </c>
       <c r="L107" s="11" t="n"/>
-      <c r="M107" s="12" t="n"/>
+      <c r="M107" s="11" t="n"/>
+      <c r="N107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -4873,9 +5416,14 @@
           <t>www.1718.ucla.edu/research/clark-dissertation-fellows</t>
         </is>
       </c>
-      <c r="K108" s="11" t="n"/>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>$36,000</t>
+        </is>
+      </c>
       <c r="L108" s="11" t="n"/>
-      <c r="M108" s="12" t="n"/>
+      <c r="M108" s="11" t="n"/>
+      <c r="N108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -4918,9 +5466,14 @@
           <t>1718.ucla.edu/research/fellowships</t>
         </is>
       </c>
-      <c r="K109" s="11" t="n"/>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>$4,000/month for 1–3 months</t>
+        </is>
+      </c>
       <c r="L109" s="11" t="n"/>
-      <c r="M109" s="12" t="n"/>
+      <c r="M109" s="11" t="n"/>
+      <c r="N109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -4959,9 +5512,14 @@
           <t>www.amsmusicology.org/funding/ams-50</t>
         </is>
       </c>
-      <c r="K110" s="11" t="n"/>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>$25,000 for one year</t>
+        </is>
+      </c>
       <c r="L110" s="11" t="n"/>
-      <c r="M110" s="12" t="n"/>
+      <c r="M110" s="11" t="n"/>
+      <c r="N110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -5004,9 +5562,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/fellowship-application</t>
         </is>
       </c>
-      <c r="K111" s="11" t="n"/>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Up to $15,000</t>
+        </is>
+      </c>
       <c r="L111" s="11" t="n"/>
-      <c r="M111" s="12" t="n"/>
+      <c r="M111" s="11" t="n"/>
+      <c r="N111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -5045,9 +5608,14 @@
           <t>grad.ucla.edu/funding/#/view-record/772/0</t>
         </is>
       </c>
-      <c r="K112" s="11" t="n"/>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>$15,000 in fees</t>
+        </is>
+      </c>
       <c r="L112" s="11" t="n"/>
-      <c r="M112" s="12" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -5086,9 +5654,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/graduate-research-mentorship-program</t>
         </is>
       </c>
-      <c r="K113" s="11" t="n"/>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
       <c r="L113" s="11" t="n"/>
-      <c r="M113" s="12" t="n"/>
+      <c r="M113" s="11" t="n"/>
+      <c r="N113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -5127,9 +5700,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/graduate-summer-research-mentorship-program</t>
         </is>
       </c>
-      <c r="K114" s="11" t="n"/>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>Summer support (varies)</t>
+        </is>
+      </c>
       <c r="L114" s="11" t="n"/>
-      <c r="M114" s="12" t="n"/>
+      <c r="M114" s="11" t="n"/>
+      <c r="N114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -5166,9 +5744,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/fellowship-application</t>
         </is>
       </c>
-      <c r="K115" s="11" t="n"/>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>Up to $6,000</t>
+        </is>
+      </c>
       <c r="L115" s="11" t="n"/>
-      <c r="M115" s="12" t="n"/>
+      <c r="M115" s="11" t="n"/>
+      <c r="N115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -5207,9 +5790,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students</t>
         </is>
       </c>
-      <c r="K116" s="11" t="n"/>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>$8,000</t>
+        </is>
+      </c>
       <c r="L116" s="11" t="n"/>
-      <c r="M116" s="12" t="n"/>
+      <c r="M116" s="11" t="n"/>
+      <c r="N116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -5246,9 +5834,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/fellowship-application</t>
         </is>
       </c>
-      <c r="K117" s="11" t="n"/>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
       <c r="L117" s="11" t="n"/>
-      <c r="M117" s="12" t="n"/>
+      <c r="M117" s="11" t="n"/>
+      <c r="N117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -5287,9 +5880,14 @@
           <t>www.hsf.net/scholarship</t>
         </is>
       </c>
-      <c r="K118" s="11" t="n"/>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>$500–$5,000 based on financial need</t>
+        </is>
+      </c>
       <c r="L118" s="11" t="n"/>
-      <c r="M118" s="12" t="n"/>
+      <c r="M118" s="11" t="n"/>
+      <c r="N118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -5332,9 +5930,14 @@
           <t>serc.si.edu/internships/opportunities</t>
         </is>
       </c>
-      <c r="K119" s="11" t="n"/>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>$700/week</t>
+        </is>
+      </c>
       <c r="L119" s="11" t="n"/>
-      <c r="M119" s="12" t="n"/>
+      <c r="M119" s="11" t="n"/>
+      <c r="N119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
@@ -5373,9 +5976,14 @@
           <t>csw.ucla.edu/funding/graduate-students/black-feminism-initiative-graduate-fellowships</t>
         </is>
       </c>
-      <c r="K120" s="11" t="n"/>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L120" s="11" t="n"/>
-      <c r="M120" s="12" t="n"/>
+      <c r="M120" s="11" t="n"/>
+      <c r="N120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
@@ -5414,9 +6022,14 @@
           <t>csw.ucla.edu/funding/graduate-students/elizabeth-blackwell-award</t>
         </is>
       </c>
-      <c r="K121" s="11" t="n"/>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>Monetary award (amount set annually by CSW)</t>
+        </is>
+      </c>
       <c r="L121" s="11" t="n"/>
-      <c r="M121" s="12" t="n"/>
+      <c r="M121" s="11" t="n"/>
+      <c r="N121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n">
@@ -5455,9 +6068,14 @@
           <t>csw.ucla.edu/funding/graduate-students/jean-stone-fellowship</t>
         </is>
       </c>
-      <c r="K122" s="11" t="n"/>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>Competitive award; amount set annually</t>
+        </is>
+      </c>
       <c r="L122" s="11" t="n"/>
-      <c r="M122" s="12" t="n"/>
+      <c r="M122" s="11" t="n"/>
+      <c r="N122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
@@ -5496,9 +6114,14 @@
           <t>csw.ucla.edu/funding/graduate-students/black-feminism-initiative-graduate-fellowships</t>
         </is>
       </c>
-      <c r="K123" s="11" t="n"/>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>$2,000</t>
+        </is>
+      </c>
       <c r="L123" s="11" t="n"/>
-      <c r="M123" s="12" t="n"/>
+      <c r="M123" s="11" t="n"/>
+      <c r="N123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n">
@@ -5537,9 +6160,14 @@
           <t>csw.ucla.edu/funding/graduate-students/paula-stone-legal-research-fellowship</t>
         </is>
       </c>
-      <c r="K124" s="11" t="n"/>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>$3,000</t>
+        </is>
+      </c>
       <c r="L124" s="11" t="n"/>
-      <c r="M124" s="12" t="n"/>
+      <c r="M124" s="11" t="n"/>
+      <c r="N124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
@@ -5576,9 +6204,14 @@
           <t>scoville.org/apply</t>
         </is>
       </c>
-      <c r="K125" s="11" t="n"/>
+      <c r="K125" s="7" t="inlineStr">
+        <is>
+          <t>Salary, health insurance, and travel covered</t>
+        </is>
+      </c>
       <c r="L125" s="11" t="n"/>
-      <c r="M125" s="12" t="n"/>
+      <c r="M125" s="11" t="n"/>
+      <c r="N125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n">
@@ -5617,9 +6250,14 @@
           <t>csw.ucla.edu/funding/graduate-students/constance-coiner-graduate-fellowship</t>
         </is>
       </c>
-      <c r="K126" s="11" t="n"/>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L126" s="11" t="n"/>
-      <c r="M126" s="12" t="n"/>
+      <c r="M126" s="11" t="n"/>
+      <c r="N126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
@@ -5658,9 +6296,14 @@
           <t>csw.ucla.edu/funding/graduate-students/penny-kanner-dissertation-research-fellowship</t>
         </is>
       </c>
-      <c r="K127" s="11" t="n"/>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L127" s="11" t="n"/>
-      <c r="M127" s="12" t="n"/>
+      <c r="M127" s="11" t="n"/>
+      <c r="N127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n">
@@ -5699,9 +6342,14 @@
           <t>www.escsi.org/escsi-john-ries-scholarship-application-2025-26</t>
         </is>
       </c>
-      <c r="K128" s="11" t="n"/>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
       <c r="L128" s="11" t="n"/>
-      <c r="M128" s="12" t="n"/>
+      <c r="M128" s="11" t="n"/>
+      <c r="N128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n">
@@ -5742,9 +6390,14 @@
           <t>linksim.org/apply</t>
         </is>
       </c>
-      <c r="K129" s="11" t="n"/>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>$35,000/year for up to 2 years</t>
+        </is>
+      </c>
       <c r="L129" s="11" t="n"/>
-      <c r="M129" s="12" t="n"/>
+      <c r="M129" s="11" t="n"/>
+      <c r="N129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
@@ -5783,9 +6436,14 @@
           <t>science.nrao.edu/opportunities/student-programs/summerstudents</t>
         </is>
       </c>
-      <c r="K130" s="11" t="n"/>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>Competitive stipend</t>
+        </is>
+      </c>
       <c r="L130" s="11" t="n"/>
-      <c r="M130" s="12" t="n"/>
+      <c r="M130" s="11" t="n"/>
+      <c r="N130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n">
@@ -5828,9 +6486,14 @@
           <t>www.lib.berkeley.edu/visit/bancroft/fellowships-awards</t>
         </is>
       </c>
-      <c r="K131" s="11" t="n"/>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L131" s="11" t="n"/>
-      <c r="M131" s="12" t="n"/>
+      <c r="M131" s="11" t="n"/>
+      <c r="N131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n">
@@ -5869,9 +6532,14 @@
           <t>international.ucla.edu/euro/funding/156750</t>
         </is>
       </c>
-      <c r="K132" s="11" t="n"/>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>Up to $5,000</t>
+        </is>
+      </c>
       <c r="L132" s="11" t="n"/>
-      <c r="M132" s="12" t="n"/>
+      <c r="M132" s="11" t="n"/>
+      <c r="N132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
@@ -5910,9 +6578,14 @@
           <t>www.international.ucla.edu/euro/funding/159538</t>
         </is>
       </c>
-      <c r="K133" s="11" t="n"/>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>Up to $4,000</t>
+        </is>
+      </c>
       <c r="L133" s="11" t="n"/>
-      <c r="M133" s="12" t="n"/>
+      <c r="M133" s="11" t="n"/>
+      <c r="N133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n">
@@ -5951,9 +6624,14 @@
           <t>www.fic.nih.gov/Programs/Pages/research-scientists.aspx</t>
         </is>
       </c>
-      <c r="K134" s="11" t="n"/>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>Salary and research support for 3-5 years</t>
+        </is>
+      </c>
       <c r="L134" s="11" t="n"/>
-      <c r="M134" s="12" t="n"/>
+      <c r="M134" s="11" t="n"/>
+      <c r="N134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
@@ -5992,9 +6670,14 @@
           <t>ccst.us/ccst-science-fellows-program</t>
         </is>
       </c>
-      <c r="K135" s="11" t="n"/>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>Competitive stipend plus health care costs</t>
+        </is>
+      </c>
       <c r="L135" s="11" t="n"/>
-      <c r="M135" s="12" t="n"/>
+      <c r="M135" s="11" t="n"/>
+      <c r="N135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n">
@@ -6033,9 +6716,14 @@
           <t>councilforeuropeanstudies.org/grants-awards-fellowships/sae-ces</t>
         </is>
       </c>
-      <c r="K136" s="11" t="n"/>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>$5,000 plus conference registration waiver</t>
+        </is>
+      </c>
       <c r="L136" s="11" t="n"/>
-      <c r="M136" s="12" t="n"/>
+      <c r="M136" s="11" t="n"/>
+      <c r="N136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n">
@@ -6072,9 +6760,14 @@
           <t>www.cement.org/education-research/pca-education-foundation</t>
         </is>
       </c>
-      <c r="K137" s="11" t="n"/>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>$35,000 total award</t>
+        </is>
+      </c>
       <c r="L137" s="11" t="n"/>
-      <c r="M137" s="12" t="n"/>
+      <c r="M137" s="11" t="n"/>
+      <c r="N137" s="12" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n">
@@ -6117,9 +6810,14 @@
           <t>www.bgu.ac.il/en/u/sde-boker/bidr/centers/bcsc</t>
         </is>
       </c>
-      <c r="K138" s="11" t="n"/>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>$26,000 annually (standard) or ~$29,000 (Distinguished); 1-2 year terms</t>
+        </is>
+      </c>
       <c r="L138" s="11" t="n"/>
-      <c r="M138" s="12" t="n"/>
+      <c r="M138" s="11" t="n"/>
+      <c r="N138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
@@ -6160,9 +6858,14 @@
           <t>fellowship-application.danonenorthamerica.com</t>
         </is>
       </c>
-      <c r="K139" s="11" t="n"/>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>$25,000 each for two recipients</t>
+        </is>
+      </c>
       <c r="L139" s="11" t="n"/>
-      <c r="M139" s="12" t="n"/>
+      <c r="M139" s="11" t="n"/>
+      <c r="N139" s="12" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n">
@@ -6205,9 +6908,14 @@
           <t>scholarships.nfb.org</t>
         </is>
       </c>
-      <c r="K140" s="11" t="n"/>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
       <c r="L140" s="11" t="n"/>
-      <c r="M140" s="12" t="n"/>
+      <c r="M140" s="11" t="n"/>
+      <c r="N140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
@@ -6248,9 +6956,14 @@
           <t>www.wri.org/update/2026-lee-schipper-memorial-scholarship-now-open-submissions</t>
         </is>
       </c>
-      <c r="K141" s="11" t="n"/>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>Up to $12,500</t>
+        </is>
+      </c>
       <c r="L141" s="11" t="n"/>
-      <c r="M141" s="12" t="n"/>
+      <c r="M141" s="11" t="n"/>
+      <c r="N141" s="12" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n">
@@ -6289,9 +7002,14 @@
           <t>cmrs.ucla.edu/awards-fellowships/white</t>
         </is>
       </c>
-      <c r="K142" s="11" t="n"/>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
       <c r="L142" s="11" t="n"/>
-      <c r="M142" s="12" t="n"/>
+      <c r="M142" s="11" t="n"/>
+      <c r="N142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n">
@@ -6330,9 +7048,14 @@
           <t>whff.org/the-program</t>
         </is>
       </c>
-      <c r="K143" s="11" t="n"/>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>GS-14 federal salary</t>
+        </is>
+      </c>
       <c r="L143" s="11" t="n"/>
-      <c r="M143" s="12" t="n"/>
+      <c r="M143" s="11" t="n"/>
+      <c r="N143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n">
@@ -6371,9 +7094,14 @@
           <t>www.international.ucla.edu/apc/article/252107</t>
         </is>
       </c>
-      <c r="K144" s="11" t="n"/>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>Up to $7,000</t>
+        </is>
+      </c>
       <c r="L144" s="11" t="n"/>
-      <c r="M144" s="12" t="n"/>
+      <c r="M144" s="11" t="n"/>
+      <c r="N144" s="12" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
@@ -6412,9 +7140,14 @@
           <t>www.1718.ucla.edu/research/ucla-graduate/graduate-certificate</t>
         </is>
       </c>
-      <c r="K145" s="11" t="n"/>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L145" s="11" t="n"/>
-      <c r="M145" s="12" t="n"/>
+      <c r="M145" s="11" t="n"/>
+      <c r="N145" s="12" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n">
@@ -6453,9 +7186,14 @@
           <t>www.afar.org/grants/afar-scholarships</t>
         </is>
       </c>
-      <c r="K146" s="11" t="n"/>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
       <c r="L146" s="11" t="n"/>
-      <c r="M146" s="12" t="n"/>
+      <c r="M146" s="11" t="n"/>
+      <c r="N146" s="12" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
@@ -6494,9 +7232,14 @@
           <t>www.simonsfoundation.org/grant/pivot-fellowship</t>
         </is>
       </c>
-      <c r="K147" s="11" t="n"/>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>Full salary support plus $10,000 allowance</t>
+        </is>
+      </c>
       <c r="L147" s="11" t="n"/>
-      <c r="M147" s="12" t="n"/>
+      <c r="M147" s="11" t="n"/>
+      <c r="N147" s="12" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n">
@@ -6535,9 +7278,14 @@
           <t>www.maldef.org/resources/scholarship-resources</t>
         </is>
       </c>
-      <c r="K148" s="11" t="n"/>
+      <c r="K148" s="7" t="inlineStr">
+        <is>
+          <t>$2,000–$10,000</t>
+        </is>
+      </c>
       <c r="L148" s="11" t="n"/>
-      <c r="M148" s="12" t="n"/>
+      <c r="M148" s="11" t="n"/>
+      <c r="N148" s="12" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n">
@@ -6578,9 +7326,14 @@
           <t>telacu.com/telacu-education-foundation/graduate-school-support/david-c-lizarraga-fellowship</t>
         </is>
       </c>
-      <c r="K149" s="11" t="n"/>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>Varies; financial support + mentorship</t>
+        </is>
+      </c>
       <c r="L149" s="11" t="n"/>
-      <c r="M149" s="12" t="n"/>
+      <c r="M149" s="11" t="n"/>
+      <c r="N149" s="12" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n">
@@ -6617,9 +7370,14 @@
           <t>www.planning.org/students/awards</t>
         </is>
       </c>
-      <c r="K150" s="11" t="n"/>
+      <c r="K150" s="7" t="inlineStr">
+        <is>
+          <t>Award amount not specified</t>
+        </is>
+      </c>
       <c r="L150" s="11" t="n"/>
-      <c r="M150" s="12" t="n"/>
+      <c r="M150" s="11" t="n"/>
+      <c r="N150" s="12" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
@@ -6658,9 +7416,14 @@
           <t>www.nationalacademies.org/programs/GULF-GULFEO-14-03</t>
         </is>
       </c>
-      <c r="K151" s="11" t="n"/>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>$76,000</t>
+        </is>
+      </c>
       <c r="L151" s="11" t="n"/>
-      <c r="M151" s="12" t="n"/>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n">
@@ -6703,9 +7466,14 @@
           <t>cisac.fsi.stanford.edu/cisac-fellowships</t>
         </is>
       </c>
-      <c r="K152" s="11" t="n"/>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>Competitive stipend for 9–11 months</t>
+        </is>
+      </c>
       <c r="L152" s="11" t="n"/>
-      <c r="M152" s="12" t="n"/>
+      <c r="M152" s="11" t="n"/>
+      <c r="N152" s="12" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n">
@@ -6744,9 +7512,14 @@
           <t>www.afar.org/grants/glenn-postdoc</t>
         </is>
       </c>
-      <c r="K153" s="11" t="n"/>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>$75,000–$80,000 per year for one year</t>
+        </is>
+      </c>
       <c r="L153" s="11" t="n"/>
-      <c r="M153" s="12" t="n"/>
+      <c r="M153" s="11" t="n"/>
+      <c r="N153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n">
@@ -6783,9 +7556,14 @@
           <t>med.stanford.edu/smisprogram.html</t>
         </is>
       </c>
-      <c r="K154" s="11" t="n"/>
+      <c r="K154" s="7" t="inlineStr">
+        <is>
+          <t>Stipend (amount not specified); full tuition and health insurance</t>
+        </is>
+      </c>
       <c r="L154" s="11" t="n"/>
-      <c r="M154" s="12" t="n"/>
+      <c r="M154" s="11" t="n"/>
+      <c r="N154" s="12" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n">
@@ -6824,9 +7602,14 @@
           <t>www.mla.org/Resources/Career/MLA-Grants-and-Awards/Edward-Guiliano-Global-Fellowships</t>
         </is>
       </c>
-      <c r="K155" s="11" t="n"/>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>Up to $2,000</t>
+        </is>
+      </c>
       <c r="L155" s="11" t="n"/>
-      <c r="M155" s="12" t="n"/>
+      <c r="M155" s="11" t="n"/>
+      <c r="N155" s="12" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n">
@@ -6867,9 +7650,14 @@
           <t>grants.nih.gov/grants/guide/pa-files/PA-25-423.html</t>
         </is>
       </c>
-      <c r="K156" s="11" t="n"/>
+      <c r="K156" s="7" t="inlineStr">
+        <is>
+          <t>Up to 3 years of support; stipend follows NIH NRSA pay scale (starting ~$56,000/year) plus institutional allowance</t>
+        </is>
+      </c>
       <c r="L156" s="11" t="n"/>
-      <c r="M156" s="12" t="n"/>
+      <c r="M156" s="11" t="n"/>
+      <c r="N156" s="12" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
@@ -6908,9 +7696,14 @@
           <t>www.damonrunyon.org/for-scientists/application-guidelines/fellowship</t>
         </is>
       </c>
-      <c r="K157" s="11" t="n"/>
+      <c r="K157" s="7" t="inlineStr">
+        <is>
+          <t>$300,000 total over 4 years ($70,000-$76,000/year plus expenses)</t>
+        </is>
+      </c>
       <c r="L157" s="11" t="n"/>
-      <c r="M157" s="12" t="n"/>
+      <c r="M157" s="11" t="n"/>
+      <c r="N157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n">
@@ -6947,9 +7740,14 @@
           <t>gfd.whoi.edu/gfd-fellowships</t>
         </is>
       </c>
-      <c r="K158" s="11" t="n"/>
+      <c r="K158" s="7" t="inlineStr">
+        <is>
+          <t>$8,430 stipend + travel allowance</t>
+        </is>
+      </c>
       <c r="L158" s="11" t="n"/>
-      <c r="M158" s="12" t="n"/>
+      <c r="M158" s="11" t="n"/>
+      <c r="N158" s="12" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n">
@@ -6992,9 +7790,14 @@
           <t>health.ucdavis.edu/mind-institute/education/postdoc-training</t>
         </is>
       </c>
-      <c r="K159" s="11" t="n"/>
+      <c r="K159" s="7" t="inlineStr">
+        <is>
+          <t>NIH-scale postdoctoral stipend + benefits for 2 years</t>
+        </is>
+      </c>
       <c r="L159" s="11" t="n"/>
-      <c r="M159" s="12" t="n"/>
+      <c r="M159" s="11" t="n"/>
+      <c r="N159" s="12" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
@@ -7033,9 +7836,14 @@
           <t>www.cancerresearch.org/cri-irvington-postdoctoral-fellowship</t>
         </is>
       </c>
-      <c r="K160" s="11" t="n"/>
+      <c r="K160" s="7" t="inlineStr">
+        <is>
+          <t>$74,000-$78,000/year</t>
+        </is>
+      </c>
       <c r="L160" s="11" t="n"/>
-      <c r="M160" s="12" t="n"/>
+      <c r="M160" s="11" t="n"/>
+      <c r="N160" s="12" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
@@ -7074,9 +7882,14 @@
           <t>www.nationalacademies.org/programs/GULF-GULFEO-14-01/application-process</t>
         </is>
       </c>
-      <c r="K161" s="11" t="n"/>
+      <c r="K161" s="7" t="inlineStr">
+        <is>
+          <t>Stipend (amount not specified)</t>
+        </is>
+      </c>
       <c r="L161" s="11" t="n"/>
-      <c r="M161" s="12" t="n"/>
+      <c r="M161" s="11" t="n"/>
+      <c r="N161" s="12" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n">
@@ -7115,9 +7928,14 @@
           <t>societyhumanities.as.cornell.edu/fellowships</t>
         </is>
       </c>
-      <c r="K162" s="11" t="n"/>
+      <c r="K162" s="7" t="inlineStr">
+        <is>
+          <t>$35,661 - $64,000 depending on fellowship type</t>
+        </is>
+      </c>
       <c r="L162" s="11" t="n"/>
-      <c r="M162" s="12" t="n"/>
+      <c r="M162" s="11" t="n"/>
+      <c r="N162" s="12" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n">
@@ -7156,9 +7974,14 @@
           <t>lucescholars.org</t>
         </is>
       </c>
-      <c r="K163" s="11" t="n"/>
+      <c r="K163" s="7" t="inlineStr">
+        <is>
+          <t>Stipends plus language training and placement support</t>
+        </is>
+      </c>
       <c r="L163" s="11" t="n"/>
-      <c r="M163" s="12" t="n"/>
+      <c r="M163" s="11" t="n"/>
+      <c r="N163" s="12" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n">
@@ -7197,9 +8020,14 @@
           <t>ucghi.universityofcalifornia.edu/fellowships/glocal-health-fellowship</t>
         </is>
       </c>
-      <c r="K164" s="11" t="n"/>
+      <c r="K164" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L164" s="11" t="n"/>
-      <c r="M164" s="12" t="n"/>
+      <c r="M164" s="11" t="n"/>
+      <c r="N164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n">
@@ -7236,9 +8064,14 @@
           <t>academy.wcfia.harvard.edu/programs/academy_scholar</t>
         </is>
       </c>
-      <c r="K165" s="11" t="n"/>
+      <c r="K165" s="7" t="inlineStr">
+        <is>
+          <t>$80,000/year + $5,000 annual research support</t>
+        </is>
+      </c>
       <c r="L165" s="11" t="n"/>
-      <c r="M165" s="12" t="n"/>
+      <c r="M165" s="11" t="n"/>
+      <c r="N165" s="12" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n">
@@ -7277,9 +8110,14 @@
           <t>www.jsps.go.jp/english/e-fellow/e-oubei-s/index.html</t>
         </is>
       </c>
-      <c r="K166" s="11" t="n"/>
+      <c r="K166" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L166" s="11" t="n"/>
-      <c r="M166" s="12" t="n"/>
+      <c r="M166" s="11" t="n"/>
+      <c r="N166" s="12" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
@@ -7318,9 +8156,14 @@
           <t>www.marshallscholarship.org</t>
         </is>
       </c>
-      <c r="K167" s="11" t="n"/>
+      <c r="K167" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L167" s="11" t="n"/>
-      <c r="M167" s="12" t="n"/>
+      <c r="M167" s="11" t="n"/>
+      <c r="N167" s="12" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n">
@@ -7359,9 +8202,14 @@
           <t>www.bwfund.org/grants/biomedical-sciences/career-awards-for-medical-scientists</t>
         </is>
       </c>
-      <c r="K168" s="11" t="n"/>
+      <c r="K168" s="7" t="inlineStr">
+        <is>
+          <t>$700,000 over 5 years</t>
+        </is>
+      </c>
       <c r="L168" s="11" t="n"/>
-      <c r="M168" s="12" t="n"/>
+      <c r="M168" s="11" t="n"/>
+      <c r="N168" s="12" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n">
@@ -7404,9 +8252,14 @@
           <t>www.wilsoncenter.org/research-fellowship</t>
         </is>
       </c>
-      <c r="K169" s="11" t="n"/>
+      <c r="K169" s="7" t="inlineStr">
+        <is>
+          <t>$90,000</t>
+        </is>
+      </c>
       <c r="L169" s="11" t="n"/>
-      <c r="M169" s="12" t="n"/>
+      <c r="M169" s="11" t="n"/>
+      <c r="N169" s="12" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n">
@@ -7445,9 +8298,14 @@
           <t>www.jfklibrary.org/archives/research-fellowships-grants</t>
         </is>
       </c>
-      <c r="K170" s="11" t="n"/>
+      <c r="K170" s="7" t="inlineStr">
+        <is>
+          <t>$3,100-$5,000</t>
+        </is>
+      </c>
       <c r="L170" s="11" t="n"/>
-      <c r="M170" s="12" t="n"/>
+      <c r="M170" s="11" t="n"/>
+      <c r="N170" s="12" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n">
@@ -7486,9 +8344,14 @@
           <t>www.surveycto.com/data-collection-research-grant</t>
         </is>
       </c>
-      <c r="K171" s="11" t="n"/>
+      <c r="K171" s="7" t="inlineStr">
+        <is>
+          <t>SurveyCTO subscription + up to $3,000 cash</t>
+        </is>
+      </c>
       <c r="L171" s="11" t="n"/>
-      <c r="M171" s="12" t="n"/>
+      <c r="M171" s="11" t="n"/>
+      <c r="N171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n">
@@ -7527,9 +8390,14 @@
           <t>www.aip.org/aip/awards/state-department-science-policy-fellowships</t>
         </is>
       </c>
-      <c r="K172" s="11" t="n"/>
+      <c r="K172" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L172" s="11" t="n"/>
-      <c r="M172" s="12" t="n"/>
+      <c r="M172" s="11" t="n"/>
+      <c r="N172" s="12" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
@@ -7568,9 +8436,14 @@
           <t>www.amphilsoc.org/grants/franklin-research-grants</t>
         </is>
       </c>
-      <c r="K173" s="11" t="n"/>
+      <c r="K173" s="7" t="inlineStr">
+        <is>
+          <t>Up to $6,500</t>
+        </is>
+      </c>
       <c r="L173" s="11" t="n"/>
-      <c r="M173" s="12" t="n"/>
+      <c r="M173" s="11" t="n"/>
+      <c r="N173" s="12" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n">
@@ -7607,9 +8480,14 @@
           <t>www.sigmaxi.org/programs/grants-in-aid-of-research</t>
         </is>
       </c>
-      <c r="K174" s="11" t="n"/>
+      <c r="K174" s="7" t="inlineStr">
+        <is>
+          <t>$500 - $5,000</t>
+        </is>
+      </c>
       <c r="L174" s="11" t="n"/>
-      <c r="M174" s="12" t="n"/>
+      <c r="M174" s="11" t="n"/>
+      <c r="N174" s="12" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
@@ -7648,9 +8526,14 @@
           <t>lsrf.org</t>
         </is>
       </c>
-      <c r="K175" s="11" t="n"/>
+      <c r="K175" s="7" t="inlineStr">
+        <is>
+          <t>$255,000 total ($85,000/year); $79,000 salary + $6,000 research allowance per year</t>
+        </is>
+      </c>
       <c r="L175" s="11" t="n"/>
-      <c r="M175" s="12" t="n"/>
+      <c r="M175" s="11" t="n"/>
+      <c r="N175" s="12" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
@@ -7689,9 +8572,14 @@
           <t>www.srf.org/programs/international-security-foreign-policy/world-politics-statecraft-fellowship</t>
         </is>
       </c>
-      <c r="K176" s="11" t="n"/>
+      <c r="K176" s="7" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
       <c r="L176" s="11" t="n"/>
-      <c r="M176" s="12" t="n"/>
+      <c r="M176" s="11" t="n"/>
+      <c r="N176" s="12" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n">
@@ -7728,9 +8616,14 @@
           <t>us.fulbrightonline.org</t>
         </is>
       </c>
-      <c r="K177" s="11" t="n"/>
+      <c r="K177" s="7" t="inlineStr">
+        <is>
+          <t>Fully funded; amounts vary by country</t>
+        </is>
+      </c>
       <c r="L177" s="11" t="n"/>
-      <c r="M177" s="12" t="n"/>
+      <c r="M177" s="11" t="n"/>
+      <c r="N177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n">
@@ -7769,9 +8662,14 @@
           <t>naeducation.org/naed-spencer-dissertation-fellowship</t>
         </is>
       </c>
-      <c r="K178" s="11" t="n"/>
+      <c r="K178" s="7" t="inlineStr">
+        <is>
+          <t>$27,500</t>
+        </is>
+      </c>
       <c r="L178" s="11" t="n"/>
-      <c r="M178" s="12" t="n"/>
+      <c r="M178" s="11" t="n"/>
+      <c r="N178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n">
@@ -7810,9 +8708,14 @@
           <t>www.spencer.org/grant_types/post-doctoral-fellowship</t>
         </is>
       </c>
-      <c r="K179" s="11" t="n"/>
+      <c r="K179" s="7" t="inlineStr">
+        <is>
+          <t>$70,000</t>
+        </is>
+      </c>
       <c r="L179" s="11" t="n"/>
-      <c r="M179" s="12" t="n"/>
+      <c r="M179" s="11" t="n"/>
+      <c r="N179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n">
@@ -7851,9 +8754,14 @@
           <t>miller.berkeley.edu/fellowship</t>
         </is>
       </c>
-      <c r="K180" s="11" t="n"/>
+      <c r="K180" s="7" t="inlineStr">
+        <is>
+          <t>$90,000 - $100,000 plus $10,000 research fund annually</t>
+        </is>
+      </c>
       <c r="L180" s="11" t="n"/>
-      <c r="M180" s="12" t="n"/>
+      <c r="M180" s="11" t="n"/>
+      <c r="N180" s="12" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n">
@@ -7890,9 +8798,14 @@
           <t>www.genome.gov/careers-training/NHGRI-Funding-Opportunities-Training-Career-Development</t>
         </is>
       </c>
-      <c r="K181" s="11" t="n"/>
+      <c r="K181" s="7" t="inlineStr">
+        <is>
+          <t>Salary and research support for 3–5 years</t>
+        </is>
+      </c>
       <c r="L181" s="11" t="n"/>
-      <c r="M181" s="12" t="n"/>
+      <c r="M181" s="11" t="n"/>
+      <c r="N181" s="12" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n">
@@ -7927,9 +8840,14 @@
           <t>cegs.ucla.edu/awards-fellowships/ahmanson</t>
         </is>
       </c>
-      <c r="K182" s="11" t="n"/>
+      <c r="K182" s="7" t="inlineStr">
+        <is>
+          <t>$3,000/month</t>
+        </is>
+      </c>
       <c r="L182" s="11" t="n"/>
-      <c r="M182" s="12" t="n"/>
+      <c r="M182" s="11" t="n"/>
+      <c r="N182" s="12" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n">
@@ -7964,9 +8882,14 @@
           <t>www.nativeforward.org/scholarship-category/graduate</t>
         </is>
       </c>
-      <c r="K183" s="11" t="n"/>
+      <c r="K183" s="7" t="inlineStr">
+        <is>
+          <t>$1,000-$5,000/year</t>
+        </is>
+      </c>
       <c r="L183" s="11" t="n"/>
-      <c r="M183" s="12" t="n"/>
+      <c r="M183" s="11" t="n"/>
+      <c r="N183" s="12" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n">
@@ -8003,9 +8926,14 @@
           <t>www.lanl.gov/engage/collaboration/internships/summer-schools/applied-machine-learning-fellowship</t>
         </is>
       </c>
-      <c r="K184" s="11" t="n"/>
+      <c r="K184" s="7" t="inlineStr">
+        <is>
+          <t>Paid fellowship plus travel reimbursement</t>
+        </is>
+      </c>
       <c r="L184" s="11" t="n"/>
-      <c r="M184" s="12" t="n"/>
+      <c r="M184" s="11" t="n"/>
+      <c r="N184" s="12" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n">
@@ -8042,9 +8970,14 @@
           <t>impactforequity.org/work-with-us/polikoff-gautreaux-fellowship</t>
         </is>
       </c>
-      <c r="K185" s="11" t="n"/>
+      <c r="K185" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L185" s="11" t="n"/>
-      <c r="M185" s="12" t="n"/>
+      <c r="M185" s="11" t="n"/>
+      <c r="N185" s="12" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n">
@@ -8081,9 +9014,14 @@
           <t>history.army.mil/html/about/df-geninfo.html</t>
         </is>
       </c>
-      <c r="K186" s="11" t="n"/>
+      <c r="K186" s="7" t="inlineStr">
+        <is>
+          <t>$15,000–$80,000 depending on fellowship tier</t>
+        </is>
+      </c>
       <c r="L186" s="11" t="n"/>
-      <c r="M186" s="12" t="n"/>
+      <c r="M186" s="11" t="n"/>
+      <c r="N186" s="12" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n">
@@ -8120,9 +9058,14 @@
           <t>www.gfoa.org/available-scholarships</t>
         </is>
       </c>
-      <c r="K187" s="11" t="n"/>
+      <c r="K187" s="7" t="inlineStr">
+        <is>
+          <t>$10,000–$20,000</t>
+        </is>
+      </c>
       <c r="L187" s="11" t="n"/>
-      <c r="M187" s="12" t="n"/>
+      <c r="M187" s="11" t="n"/>
+      <c r="N187" s="12" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n">
@@ -8159,9 +9102,14 @@
           <t>www.middlebury.edu/language-schools/funding/fellowships-scholarships/peace</t>
         </is>
       </c>
-      <c r="K188" s="11" t="n"/>
+      <c r="K188" s="7" t="inlineStr">
+        <is>
+          <t>Full tuition, housing, and food for summer</t>
+        </is>
+      </c>
       <c r="L188" s="11" t="n"/>
-      <c r="M188" s="12" t="n"/>
+      <c r="M188" s="11" t="n"/>
+      <c r="N188" s="12" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n">
@@ -8202,9 +9150,14 @@
           <t>fellowships.si.edu/opportunity/fellowships-museum-practice-fmp</t>
         </is>
       </c>
-      <c r="K189" s="11" t="n"/>
+      <c r="K189" s="7" t="inlineStr">
+        <is>
+          <t>$3,500 per month plus round-trip travel to Washington DC</t>
+        </is>
+      </c>
       <c r="L189" s="11" t="n"/>
-      <c r="M189" s="12" t="n"/>
+      <c r="M189" s="11" t="n"/>
+      <c r="N189" s="12" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n">
@@ -8241,9 +9194,14 @@
           <t>www.acrpacademic.org</t>
         </is>
       </c>
-      <c r="K190" s="11" t="n"/>
+      <c r="K190" s="7" t="inlineStr">
+        <is>
+          <t>$12,000 per award (up to 10 awards)</t>
+        </is>
+      </c>
       <c r="L190" s="11" t="n"/>
-      <c r="M190" s="12" t="n"/>
+      <c r="M190" s="11" t="n"/>
+      <c r="N190" s="12" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n">
@@ -8280,9 +9238,14 @@
           <t>ldft.huji.ac.il</t>
         </is>
       </c>
-      <c r="K191" s="11" t="n"/>
+      <c r="K191" s="7" t="inlineStr">
+        <is>
+          <t>Monthly stipend scaled to field and stage; housing assistance provided</t>
+        </is>
+      </c>
       <c r="L191" s="11" t="n"/>
-      <c r="M191" s="12" t="n"/>
+      <c r="M191" s="11" t="n"/>
+      <c r="N191" s="12" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n">
@@ -8319,9 +9282,14 @@
           <t>www.agu.org/honors/horton-grant</t>
         </is>
       </c>
-      <c r="K192" s="11" t="n"/>
+      <c r="K192" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L192" s="11" t="n"/>
-      <c r="M192" s="12" t="n"/>
+      <c r="M192" s="11" t="n"/>
+      <c r="N192" s="12" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n">
@@ -8358,9 +9326,14 @@
           <t>www.crs.org/about/careers/fellowships</t>
         </is>
       </c>
-      <c r="K193" s="11" t="n"/>
+      <c r="K193" s="7" t="inlineStr">
+        <is>
+          <t>Living stipend + housing + benefits for 12 months</t>
+        </is>
+      </c>
       <c r="L193" s="11" t="n"/>
-      <c r="M193" s="12" t="n"/>
+      <c r="M193" s="11" t="n"/>
+      <c r="N193" s="12" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n">
@@ -8397,9 +9370,14 @@
           <t>www.mfah.org/fellowships</t>
         </is>
       </c>
-      <c r="K194" s="11" t="n"/>
+      <c r="K194" s="7" t="inlineStr">
+        <is>
+          <t>$5,500</t>
+        </is>
+      </c>
       <c r="L194" s="11" t="n"/>
-      <c r="M194" s="12" t="n"/>
+      <c r="M194" s="11" t="n"/>
+      <c r="N194" s="12" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n">
@@ -8434,9 +9412,14 @@
           <t>www.jfklibrary.org/about-us/jobs-internships-volunteers/internship-types</t>
         </is>
       </c>
-      <c r="K195" s="11" t="n"/>
+      <c r="K195" s="7" t="inlineStr">
+        <is>
+          <t>Stipend (amount not specified)</t>
+        </is>
+      </c>
       <c r="L195" s="11" t="n"/>
-      <c r="M195" s="12" t="n"/>
+      <c r="M195" s="11" t="n"/>
+      <c r="N195" s="12" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n">
@@ -8473,9 +9456,14 @@
           <t>cbd.cmu.edu/join-us/lane-fellow.html</t>
         </is>
       </c>
-      <c r="K196" s="11" t="n"/>
+      <c r="K196" s="7" t="inlineStr">
+        <is>
+          <t>$65,000/year stipend + $3,000 professional support + benefits for 3 years</t>
+        </is>
+      </c>
       <c r="L196" s="11" t="n"/>
-      <c r="M196" s="12" t="n"/>
+      <c r="M196" s="11" t="n"/>
+      <c r="N196" s="12" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n">
@@ -8512,9 +9500,14 @@
           <t>www.metmuseum.org/opportunities/fellowships/leonard-a-lauder-fellowships-in-modern-art</t>
         </is>
       </c>
-      <c r="K197" s="11" t="n"/>
+      <c r="K197" s="7" t="inlineStr">
+        <is>
+          <t>$6,000 travel stipend; additional stipend varies by fellowship type</t>
+        </is>
+      </c>
       <c r="L197" s="11" t="n"/>
-      <c r="M197" s="12" t="n"/>
+      <c r="M197" s="11" t="n"/>
+      <c r="N197" s="12" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n">
@@ -8551,9 +9544,14 @@
           <t>www.usgs.gov/centers/mendenhall-research-fellowship-program</t>
         </is>
       </c>
-      <c r="K198" s="11" t="n"/>
+      <c r="K198" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="L198" s="11" t="n"/>
-      <c r="M198" s="12" t="n"/>
+      <c r="M198" s="11" t="n"/>
+      <c r="N198" s="12" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n">
@@ -8590,9 +9588,14 @@
           <t>www.physiology.org/professional-development/awards/trainees/porter_fellowship</t>
         </is>
       </c>
-      <c r="K199" s="11" t="n"/>
+      <c r="K199" s="7" t="inlineStr">
+        <is>
+          <t>$28,300/year stipend + $2,500 research allowance</t>
+        </is>
+      </c>
       <c r="L199" s="11" t="n"/>
-      <c r="M199" s="12" t="n"/>
+      <c r="M199" s="11" t="n"/>
+      <c r="N199" s="12" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n">
@@ -8629,9 +9632,14 @@
           <t>orise.orau.gov/tsl/index.html</t>
         </is>
       </c>
-      <c r="K200" s="11" t="n"/>
+      <c r="K200" s="7" t="inlineStr">
+        <is>
+          <t>Competitive stipend commensurate with experience</t>
+        </is>
+      </c>
       <c r="L200" s="11" t="n"/>
-      <c r="M200" s="12" t="n"/>
+      <c r="M200" s="11" t="n"/>
+      <c r="N200" s="12" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n">
@@ -8668,9 +9676,14 @@
           <t>www.ioes.ucla.edu/jobs/the-2027-ucla-la-kretz-center-postdoctoral-fellowship-in-california-conservation-science</t>
         </is>
       </c>
-      <c r="K201" s="11" t="n"/>
+      <c r="K201" s="7" t="inlineStr">
+        <is>
+          <t>Competitive salary, full benefits, and $7,500 research/travel allowance</t>
+        </is>
+      </c>
       <c r="L201" s="11" t="n"/>
-      <c r="M201" s="12" t="n"/>
+      <c r="M201" s="11" t="n"/>
+      <c r="N201" s="12" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n">
@@ -8707,9 +9720,14 @@
           <t>med.stanford.edu/prevention/education/fellowship.html</t>
         </is>
       </c>
-      <c r="K202" s="11" t="n"/>
+      <c r="K202" s="7" t="inlineStr">
+        <is>
+          <t>NIH NRSA stipend scale + benefits</t>
+        </is>
+      </c>
       <c r="L202" s="11" t="n"/>
-      <c r="M202" s="12" t="n"/>
+      <c r="M202" s="11" t="n"/>
+      <c r="N202" s="12" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n">
@@ -8746,9 +9764,14 @@
           <t>aefpweb.org/funding-opportunities</t>
         </is>
       </c>
-      <c r="K203" s="11" t="n"/>
+      <c r="K203" s="7" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
       <c r="L203" s="11" t="n"/>
-      <c r="M203" s="12" t="n"/>
+      <c r="M203" s="11" t="n"/>
+      <c r="N203" s="12" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n">
@@ -8785,9 +9808,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-entering-students/fellowships-grants</t>
         </is>
       </c>
-      <c r="K204" s="11" t="n"/>
+      <c r="K204" s="7" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
       <c r="L204" s="11" t="n"/>
-      <c r="M204" s="12" t="n"/>
+      <c r="M204" s="11" t="n"/>
+      <c r="N204" s="12" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="n">
@@ -8822,9 +9850,14 @@
           <t>www.symposium.org/competition</t>
         </is>
       </c>
-      <c r="K205" s="11" t="n"/>
+      <c r="K205" s="7" t="inlineStr">
+        <is>
+          <t>CHF 20,000 in prize money shared by top winners</t>
+        </is>
+      </c>
       <c r="L205" s="11" t="n"/>
-      <c r="M205" s="12" t="n"/>
+      <c r="M205" s="11" t="n"/>
+      <c r="N205" s="12" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="n">
@@ -8859,19 +9892,24 @@
           <t>aaas.dartmouth.edu/research/thurgood-marshall-dissertation-and-postdoctoral-fellowship</t>
         </is>
       </c>
-      <c r="K206" s="11" t="n"/>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>$49,860 (predoctoral) + $67,580 (postdoctoral) plus benefits</t>
+        </is>
+      </c>
       <c r="L206" s="11" t="n"/>
-      <c r="M206" s="12" t="n"/>
+      <c r="M206" s="11" t="n"/>
+      <c r="N206" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M206"/>
-  <conditionalFormatting sqref="A2:L206">
+  <autoFilter ref="A1:N206"/>
+  <conditionalFormatting sqref="A2:M206">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$L2&lt;&gt;""</formula>
+      <formula>$M2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L206" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M206" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Entered,Already up to date,Sponsor page differs,Record not found"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9092,7 +10130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9101,9 +10139,10 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -9137,17 +10176,22 @@
           <t>Researched website</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Award amount</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Backend shows</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -9176,9 +10220,14 @@
           <t>www.whoi.edu/what-we-do/educate/postdoctoral/postdocs-scholar-fellowship-appointments/apo-postdoctoral-scholar</t>
         </is>
       </c>
-      <c r="G2" s="11" t="n"/>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>At least $71,000/year for 18 months plus benefits</t>
+        </is>
+      </c>
       <c r="H2" s="11" t="n"/>
-      <c r="I2" s="12" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -9203,9 +10252,14 @@
           <t>americanart.si.edu/research/fellowships/apply</t>
         </is>
       </c>
-      <c r="G3" s="11" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>$10,000 for 10-week graduate fellows; $45,000/year for predoctoral fellows; $57,000/year for postdoctoral and senior fellows (prorated for shorter terms)</t>
+        </is>
+      </c>
       <c r="H3" s="11" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -9230,9 +10284,14 @@
           <t>shc.stanford.edu/stanford-humanities-center/fellowships/mellon-fellowship-scholars-humanities</t>
         </is>
       </c>
-      <c r="G4" s="11" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>$98,000 stipend/year plus $6,000 research account and $9,000 moving stipend</t>
+        </is>
+      </c>
       <c r="H4" s="11" t="n"/>
-      <c r="I4" s="12" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -9257,9 +10316,14 @@
           <t>fellowships.si.edu/fellowship-programs</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>$10,000-$57,000 annualized stipend depending on level</t>
+        </is>
+      </c>
       <c r="H5" s="11" t="n"/>
-      <c r="I5" s="12" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -9284,9 +10348,14 @@
           <t>www.acls.org/competitions/the-robert-h-n-ho-family-foundation-dissertation-fellowships-in-buddhist-studies</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>$35,000 plus up to $5,000 supplement</t>
+        </is>
+      </c>
       <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -9311,9 +10380,14 @@
           <t>www.daad.org/en/find-funding/graduate-opportunities/research-grants/german-studies-research-grants</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>$2,000-$3,000</t>
+        </is>
+      </c>
       <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -9338,9 +10412,14 @@
           <t>lsa.umich.edu/daas/graduates/fellowship-and-grant-funding/du-bois-mandela-rodney-post-doctoral-fellowship.html</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>$56,000 package ($52,000 stipend + benefits, $3,000 research/travel, $1,000 relocation)</t>
+        </is>
+      </c>
       <c r="H8" s="11" t="n"/>
-      <c r="I8" s="12" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -9365,9 +10444,14 @@
           <t>sarweb.org/scholars/resident</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="12" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -9392,9 +10476,14 @@
           <t>www.getty.edu/projects/graduate-internships</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>$52,500 for 12 months plus $1,500 relocation</t>
+        </is>
+      </c>
       <c r="H10" s="11" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -9419,9 +10508,14 @@
           <t>science.osti.gov/wdts/scgsr</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Up to $3,000/month stipend + up to $2,000 travel reimbursement</t>
+        </is>
+      </c>
       <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -9446,9 +10540,14 @@
           <t>csw.ucla.edu/funding/travel-grants</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -9473,9 +10572,14 @@
           <t>www.grahamfoundation.org/grant_programs/?mode=award</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H13" s="11" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -9500,9 +10604,14 @@
           <t>employment.williams.edu/faculty-positions</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>$60,000 annual stipend (2027 cohort)</t>
+        </is>
+      </c>
       <c r="H14" s="11" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -9527,9 +10636,14 @@
           <t>afsp.org/research-grant-information</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Up to $140,000 over 2 years ($56,000/year stipend + $14,000/year institutional allowance)</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="12" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -9554,9 +10668,14 @@
           <t>www.amnh.org/research/richard-gilder-graduate-school/fellowships</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H16" s="11" t="n"/>
-      <c r="I16" s="12" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -9581,9 +10700,14 @@
           <t>clscholarship.org/apply</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Fully funded (travel, tuition, room/board covered)</t>
+        </is>
+      </c>
       <c r="H17" s="11" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -9608,9 +10732,14 @@
           <t>www.newberry.org/research/fellowships/long-term-fellowships</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>$5,000/month stipend</t>
+        </is>
+      </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -9635,9 +10764,14 @@
           <t>mahindrahumanities.harvard.edu/postdoctoral-fellowships</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H19" s="11" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -9662,9 +10796,14 @@
           <t>www.kressfoundation.org/Programs/Fellowships/History-of-Art-Institutional-Fellowships</t>
         </is>
       </c>
-      <c r="G20" s="11" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>$45,000/year starting fall 2026</t>
+        </is>
+      </c>
       <c r="H20" s="11" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -9689,9 +10828,14 @@
           <t>grassfoundation.org/apply-for-the-2027-grass-fellowship</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -9716,9 +10860,14 @@
           <t>www.nypl.org/about/fellowships-institutes/schomburg-center-scholars-in-residency</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H22" s="11" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -9743,9 +10892,14 @@
           <t>www.fu-berlin.de/en/sites/bprogram/index.html</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H23" s="11" t="n"/>
-      <c r="I23" s="12" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -9770,9 +10924,14 @@
           <t>www.smartscholarship.org/smart/en</t>
         </is>
       </c>
-      <c r="G24" s="11" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Full tuition, annual stipend, health insurance allowance, book allowance, and paid summer internships</t>
+        </is>
+      </c>
       <c r="H24" s="11" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -9797,9 +10956,14 @@
           <t>www.blakemorefoundation.org/blakemorefreeman</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Full tuition plus stipend for living, travel, and study expenses</t>
+        </is>
+      </c>
       <c r="H25" s="11" t="n"/>
-      <c r="I25" s="12" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -9824,9 +10988,14 @@
           <t>www.udall.gov/OurPrograms/Internship/ImportantDates.aspx</t>
         </is>
       </c>
-      <c r="G26" s="11" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Paid stipend, travel, and housing covered</t>
+        </is>
+      </c>
       <c r="H26" s="11" t="n"/>
-      <c r="I26" s="12" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -9851,9 +11020,14 @@
           <t>acorjordan.org/caorc-fellowships</t>
         </is>
       </c>
-      <c r="G27" s="11" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H27" s="11" t="n"/>
-      <c r="I27" s="12" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -9878,9 +11052,14 @@
           <t>acsus.org/acsus-enders-graduate-fellowship</t>
         </is>
       </c>
-      <c r="G28" s="11" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
       <c r="H28" s="11" t="n"/>
-      <c r="I28" s="12" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -9905,9 +11084,14 @@
           <t>fulbright.wisc.edu/ddra</t>
         </is>
       </c>
-      <c r="G29" s="11" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H29" s="11" t="n"/>
-      <c r="I29" s="12" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -9932,9 +11116,14 @@
           <t>astrobiology.nasa.gov/research/astrobiology-at-nasa/exobiology</t>
         </is>
       </c>
-      <c r="G30" s="11" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Varies by award; typical multi-year research grant</t>
+        </is>
+      </c>
       <c r="H30" s="11" t="n"/>
-      <c r="I30" s="12" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -9959,9 +11148,14 @@
           <t>www.icwa.org/apply</t>
         </is>
       </c>
-      <c r="G31" s="11" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H31" s="11" t="n"/>
-      <c r="I31" s="12" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -9986,9 +11180,14 @@
           <t>en.kf.or.kr</t>
         </is>
       </c>
-      <c r="G32" s="11" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="12" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -10013,9 +11212,14 @@
           <t>en.scholion.huji.ac.il/mandel-postdoctoral-fellowship</t>
         </is>
       </c>
-      <c r="G33" s="11" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Approx. 138,000 NIS/year plus research budget</t>
+        </is>
+      </c>
       <c r="H33" s="11" t="n"/>
-      <c r="I33" s="12" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -10040,9 +11244,14 @@
           <t>proposals.nycommunitytrust.org/Rfp/DownloadRfp/?id=102</t>
         </is>
       </c>
-      <c r="G34" s="11" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>$100,000-$250,000 total over two years</t>
+        </is>
+      </c>
       <c r="H34" s="11" t="n"/>
-      <c r="I34" s="12" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -10067,9 +11276,14 @@
           <t>postdocs.upenn.edu/provosts-fellowship/provosts-postdoctoral-fellowship</t>
         </is>
       </c>
-      <c r="G35" s="11" t="n"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>$68,300 stipend in year one (increasing $2,000/year), plus a $7,000/year research and travel allowance and up to $5,000 relocation allowance</t>
+        </is>
+      </c>
       <c r="H35" s="11" t="n"/>
-      <c r="I35" s="12" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -10094,9 +11308,14 @@
           <t>www.metmuseum.org/opportunities/fellowships/fellowship-in-history-of-art-and-visual-culture</t>
         </is>
       </c>
-      <c r="G36" s="11" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>$53,000 (junior fellows) or $63,000 (senior fellows), plus a $6,000 travel stipend</t>
+        </is>
+      </c>
       <c r="H36" s="11" t="n"/>
-      <c r="I36" s="12" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -10121,9 +11340,14 @@
           <t>www.getty.edu/projects/postdoctoral-fellowship-conservation-science</t>
         </is>
       </c>
-      <c r="G37" s="11" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Annual stipend, health insurance, study-trip allowance, and Getty scholar housing (specific dollar amount not stated)</t>
+        </is>
+      </c>
       <c r="H37" s="11" t="n"/>
-      <c r="I37" s="12" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -10148,9 +11372,14 @@
           <t>faa.illinois.edu/research/research-funding-resources/kate-neal-kinley-memorial-fellowship</t>
         </is>
       </c>
-      <c r="G38" s="11" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>$20,000 (art/design, dance, music, or theatre award)</t>
+        </is>
+      </c>
       <c r="H38" s="11" t="n"/>
-      <c r="I38" s="12" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -10175,9 +11404,14 @@
           <t>www.wesleyan.edu/humanities/fellowships/mellon.html</t>
         </is>
       </c>
-      <c r="G39" s="11" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>$70,000 annual stipend plus $3,000 research funds</t>
+        </is>
+      </c>
       <c r="H39" s="11" t="n"/>
-      <c r="I39" s="12" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -10202,9 +11436,14 @@
           <t>ucnature.org/research/student-research-funding/mathias-grant</t>
         </is>
       </c>
-      <c r="G40" s="11" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Up to $3,000 per grant (approx. $38,000 total pool)</t>
+        </is>
+      </c>
       <c r="H40" s="11" t="n"/>
-      <c r="I40" s="12" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -10229,9 +11468,14 @@
           <t>uchri.org/grants/medicine-humanities-the-andrew-vincent-white-and-florence-wales-white-graduate-student-scholarship-2026-27</t>
         </is>
       </c>
-      <c r="G41" s="11" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Up to $27,000</t>
+        </is>
+      </c>
       <c r="H41" s="11" t="n"/>
-      <c r="I41" s="12" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -10256,9 +11500,14 @@
           <t>chateaubriand-fellowship.org/stem-application</t>
         </is>
       </c>
-      <c r="G42" s="11" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Up to €1,850/month</t>
+        </is>
+      </c>
       <c r="H42" s="11" t="n"/>
-      <c r="I42" s="12" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -10283,9 +11532,14 @@
           <t>simpler.grants.gov/opportunity/63365b72-6e30-493e-ab12-9e22aff4d17e</t>
         </is>
       </c>
-      <c r="G43" s="11" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H43" s="11" t="n"/>
-      <c r="I43" s="12" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -10310,9 +11564,14 @@
           <t>www.international.ucla.edu/apc/funding</t>
         </is>
       </c>
-      <c r="G44" s="11" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H44" s="11" t="n"/>
-      <c r="I44" s="12" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -10337,9 +11596,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/fellowship-application</t>
         </is>
       </c>
-      <c r="G45" s="11" t="n"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H45" s="11" t="n"/>
-      <c r="I45" s="12" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -10364,9 +11628,14 @@
           <t>grad.ucla.edu/funding/financial-aid/funding-for-continuing-students/fellowship-application</t>
         </is>
       </c>
-      <c r="G46" s="11" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H46" s="11" t="n"/>
-      <c r="I46" s="12" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -10391,9 +11660,14 @@
           <t>www.csustan.edu/graduate-studies-research/student-opportunities/chancellors-doctoral-incentive-program-cdip</t>
         </is>
       </c>
-      <c r="G47" s="11" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Up to $10,000/year for 3 years (max $30,000), forgivable at 20%/year of full-time CSU teaching employment</t>
+        </is>
+      </c>
       <c r="H47" s="11" t="n"/>
-      <c r="I47" s="12" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -10418,9 +11692,14 @@
           <t>www.geosociety.org/grants-scholarships/graduate-research</t>
         </is>
       </c>
-      <c r="G48" s="11" t="n"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>$7,500 (ExxonMobil-sponsored awards); other GSA research grants vary</t>
+        </is>
+      </c>
       <c r="H48" s="11" t="n"/>
-      <c r="I48" s="12" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -10445,9 +11724,14 @@
           <t>www.international.ucla.edu/japan/internalfunding</t>
         </is>
       </c>
-      <c r="G49" s="11" t="n"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Up to $8,000</t>
+        </is>
+      </c>
       <c r="H49" s="11" t="n"/>
-      <c r="I49" s="12" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -10472,9 +11756,14 @@
           <t>www.international.ucla.edu/japan/internalfunding</t>
         </is>
       </c>
-      <c r="G50" s="11" t="n"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>$25,000</t>
+        </is>
+      </c>
       <c r="H50" s="11" t="n"/>
-      <c r="I50" s="12" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -10499,9 +11788,14 @@
           <t>www.international.ucla.edu/japan/internalfunding</t>
         </is>
       </c>
-      <c r="G51" s="11" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>$10,000</t>
+        </is>
+      </c>
       <c r="H51" s="11" t="n"/>
-      <c r="I51" s="12" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -10526,9 +11820,14 @@
           <t>royalsociety.org/grants/newton-international</t>
         </is>
       </c>
-      <c r="G52" s="11" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Funding cap of £280,000 (Royal Society scheme)</t>
+        </is>
+      </c>
       <c r="H52" s="11" t="n"/>
-      <c r="I52" s="12" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -10553,9 +11852,14 @@
           <t>islamicscholarshipfund.org</t>
         </is>
       </c>
-      <c r="G53" s="11" t="n"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Varies by fellowship ($40,000 Congressional; $10,000+ Journalism)</t>
+        </is>
+      </c>
       <c r="H53" s="11" t="n"/>
-      <c r="I53" s="12" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -10580,9 +11884,14 @@
           <t>www2.hao.ucar.edu/about/visitor-program/newkirk-fellowship</t>
         </is>
       </c>
-      <c r="G54" s="11" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H54" s="11" t="n"/>
-      <c r="I54" s="12" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -10607,9 +11916,14 @@
           <t>invention.si.edu/lemelson-center-fellowship-program</t>
         </is>
       </c>
-      <c r="G55" s="11" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H55" s="11" t="n"/>
-      <c r="I55" s="12" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -10634,9 +11948,14 @@
           <t>nhsc.hrsa.gov/scholarships/how-to-apply</t>
         </is>
       </c>
-      <c r="G56" s="11" t="n"/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Full tuition/fees plus a monthly stipend</t>
+        </is>
+      </c>
       <c r="H56" s="11" t="n"/>
-      <c r="I56" s="12" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -10661,9 +11980,14 @@
           <t>www.neh.gov/grants/research/fellowships</t>
         </is>
       </c>
-      <c r="G57" s="11" t="n"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Up to $60,000 ($5,000/month for 6–12 months)</t>
+        </is>
+      </c>
       <c r="H57" s="11" t="n"/>
-      <c r="I57" s="12" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -10688,9 +12012,14 @@
           <t>greatmindsinstem.org/gmis-scholarship-application/gmis-scholarships</t>
         </is>
       </c>
-      <c r="G58" s="11" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>$500-$10,000</t>
+        </is>
+      </c>
       <c r="H58" s="11" t="n"/>
-      <c r="I58" s="12" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -10715,9 +12044,14 @@
           <t>www.ashfoundation.org/apply/graduate-student-scholarship</t>
         </is>
       </c>
-      <c r="G59" s="11" t="n"/>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
       <c r="H59" s="11" t="n"/>
-      <c r="I59" s="12" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -10742,9 +12076,14 @@
           <t>mirzayanfellow.nas.edu</t>
         </is>
       </c>
-      <c r="G60" s="11" t="n"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H60" s="11" t="n"/>
-      <c r="I60" s="12" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -10769,9 +12108,14 @@
           <t>seagrant.noaa.gov/communities/students/graduate-fellows/knauss-fellowship-program/prospective</t>
         </is>
       </c>
-      <c r="G61" s="11" t="n"/>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Paid one-year fellowship with salary and benefits</t>
+        </is>
+      </c>
       <c r="H61" s="11" t="n"/>
-      <c r="I61" s="12" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -10796,9 +12140,14 @@
           <t>www.invent.org/collegiate-inventors</t>
         </is>
       </c>
-      <c r="G62" s="11" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Up to $15,000</t>
+        </is>
+      </c>
       <c r="H62" s="11" t="n"/>
-      <c r="I62" s="12" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -10823,9 +12172,14 @@
           <t>www.us.emb-japan.go.jp/itpr_en/mext-scholarship.html</t>
         </is>
       </c>
-      <c r="G63" s="11" t="n"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Full tuition + monthly stipend + round-trip airfare</t>
+        </is>
+      </c>
       <c r="H63" s="11" t="n"/>
-      <c r="I63" s="12" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -10850,9 +12204,14 @@
           <t>caseagrant.ucsd.edu/funding/2027-california-sea-grant-state-fellowship</t>
         </is>
       </c>
-      <c r="G64" s="11" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H64" s="11" t="n"/>
-      <c r="I64" s="12" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -10877,9 +12236,14 @@
           <t>hhwf.org/research-fellowship</t>
         </is>
       </c>
-      <c r="G65" s="11" t="n"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>$229,500 over 3 years</t>
+        </is>
+      </c>
       <c r="H65" s="11" t="n"/>
-      <c r="I65" s="12" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -10904,9 +12268,14 @@
           <t>cgsnet.org/about/awards/cgs-proquest-distinguished-dissertation</t>
         </is>
       </c>
-      <c r="G66" s="11" t="n"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>$2,000</t>
+        </is>
+      </c>
       <c r="H66" s="11" t="n"/>
-      <c r="I66" s="12" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -10931,9 +12300,14 @@
           <t>professional.heart.org/en/research-programs/aha-funding-opportunities/predoctoral-fellowship</t>
         </is>
       </c>
-      <c r="G67" s="11" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>$29,364/year stipend plus $4,550 health insurance and $2,000 project support</t>
+        </is>
+      </c>
       <c r="H67" s="11" t="n"/>
-      <c r="I67" s="12" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -10958,9 +12332,14 @@
           <t>sf.princeton.edu/application</t>
         </is>
       </c>
-      <c r="G68" s="11" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H68" s="11" t="n"/>
-      <c r="I68" s="12" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -10985,9 +12364,14 @@
           <t>www.asanet.org/academic-professional-resources/asa-grants-and-fellowships/community-action-research-initiative-grants</t>
         </is>
       </c>
-      <c r="G69" s="11" t="n"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Up to $3,000 per project</t>
+        </is>
+      </c>
       <c r="H69" s="11" t="n"/>
-      <c r="I69" s="12" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -11012,9 +12396,14 @@
           <t>research.ibm.com/university/awards/fellowships-faq.html</t>
         </is>
       </c>
-      <c r="G70" s="11" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H70" s="11" t="n"/>
-      <c r="I70" s="12" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -11039,9 +12428,14 @@
           <t>careers.state.gov/interns-fellows/student-internship-program</t>
         </is>
       </c>
-      <c r="G71" s="11" t="n"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Paid position (hourly wage varies by role)</t>
+        </is>
+      </c>
       <c r="H71" s="11" t="n"/>
-      <c r="I71" s="12" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -11066,9 +12460,14 @@
           <t>www.beckman-foundation.org/programs/beckman-postdoctoral-fellows</t>
         </is>
       </c>
-      <c r="G72" s="11" t="n"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>$224,000 over 2 years (salary, benefits, research funds); instrumentation track adds up to $200,000 one-time for equipment/development</t>
+        </is>
+      </c>
       <c r="H72" s="11" t="n"/>
-      <c r="I72" s="12" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -11093,9 +12492,14 @@
           <t>www.international.ucla.edu/israel/funding</t>
         </is>
       </c>
-      <c r="G73" s="11" t="n"/>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H73" s="11" t="n"/>
-      <c r="I73" s="12" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -11120,9 +12524,14 @@
           <t>commonfund.nih.gov/earlyindependence</t>
         </is>
       </c>
-      <c r="G74" s="11" t="n"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H74" s="11" t="n"/>
-      <c r="I74" s="12" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -11147,9 +12556,14 @@
           <t>www.radcliffe.harvard.edu/radcliffe-fellowship/application-information</t>
         </is>
       </c>
-      <c r="G75" s="11" t="n"/>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>$78,000 stipend + $5,000 project expense fund</t>
+        </is>
+      </c>
       <c r="H75" s="11" t="n"/>
-      <c r="I75" s="12" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -11174,9 +12588,14 @@
           <t>www.helsinki.fi/en/helsinki-collegium-advanced-studies/apply/apply-hcas-core-fellowship</t>
         </is>
       </c>
-      <c r="G76" s="11" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H76" s="11" t="n"/>
-      <c r="I76" s="12" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -11201,9 +12620,14 @@
           <t>societyoffellows.umich.edu/the-fellowship/application-guidelines</t>
         </is>
       </c>
-      <c r="G77" s="11" t="n"/>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H77" s="11" t="n"/>
-      <c r="I77" s="12" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -11228,9 +12652,14 @@
           <t>www.americanacademy.de/apply/apply-for-a-fellowship</t>
         </is>
       </c>
-      <c r="G78" s="11" t="n"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>$5,000 monthly stipend plus room, board, and travel</t>
+        </is>
+      </c>
       <c r="H78" s="11" t="n"/>
-      <c r="I78" s="12" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -11255,9 +12684,14 @@
           <t>americanaustralian.org/scholarships/education-fund</t>
         </is>
       </c>
-      <c r="G79" s="11" t="n"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Up to $40,000 (tuition and living expenses)</t>
+        </is>
+      </c>
       <c r="H79" s="11" t="n"/>
-      <c r="I79" s="12" t="n"/>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -11282,9 +12716,14 @@
           <t>st.llnl.gov/opportunities/postdocs/postdoc-program/lawrence-fellowship</t>
         </is>
       </c>
-      <c r="G80" s="11" t="n"/>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>$12,235/month; 3-year appointment</t>
+        </is>
+      </c>
       <c r="H80" s="11" t="n"/>
-      <c r="I80" s="12" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -11309,9 +12748,14 @@
           <t>www.aacu.org/about/awards/the-k-patricia-cross-future-leaders-award</t>
         </is>
       </c>
-      <c r="G81" s="11" t="n"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Complimentary conference registration, one-year AAC&amp;U membership, and Liberal Education subscription (no cash award; travel/lodging not covered)</t>
+        </is>
+      </c>
       <c r="H81" s="11" t="n"/>
-      <c r="I81" s="12" t="n"/>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -11334,9 +12778,14 @@
           <t>arce.org/fellowships-landing</t>
         </is>
       </c>
-      <c r="G82" s="11" t="n"/>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H82" s="11" t="n"/>
-      <c r="I82" s="12" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -11359,9 +12808,14 @@
           <t>www.medievalacademy.org/page/Baldwin_Fellowship</t>
         </is>
       </c>
-      <c r="G83" s="11" t="n"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>$20,000/year for up to 2 years</t>
+        </is>
+      </c>
       <c r="H83" s="11" t="n"/>
-      <c r="I83" s="12" t="n"/>
+      <c r="I83" s="11" t="n"/>
+      <c r="J83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -11384,9 +12838,14 @@
           <t>theccwh.org/ccwh-awards/catherine-prelinger-award</t>
         </is>
       </c>
-      <c r="G84" s="11" t="n"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>$20,000</t>
+        </is>
+      </c>
       <c r="H84" s="11" t="n"/>
-      <c r="I84" s="12" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -11413,9 +12872,14 @@
           <t>annasobollevyfoundation.org/how-to-apply</t>
         </is>
       </c>
-      <c r="G85" s="11" t="n"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Up to $18,000/year tuition</t>
+        </is>
+      </c>
       <c r="H85" s="11" t="n"/>
-      <c r="I85" s="12" t="n"/>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -11438,9 +12902,14 @@
           <t>www.aera.net/Professional-Opportunities-Funding/AERA-Funding-Opportunities/AERA-NSF-Grants-Program/Dissertation-Grants</t>
         </is>
       </c>
-      <c r="G86" s="11" t="n"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H86" s="11" t="n"/>
-      <c r="I86" s="12" t="n"/>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -11467,9 +12936,14 @@
           <t>www.aei.org/special-features/jeane-kirkpatrick-fellowship-program</t>
         </is>
       </c>
-      <c r="G87" s="11" t="n"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H87" s="11" t="n"/>
-      <c r="I87" s="12" t="n"/>
+      <c r="I87" s="11" t="n"/>
+      <c r="J87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -11492,9 +12966,14 @@
           <t>www.amstat.org/ASA/Your-Career/ASA-Fellowships-and-Grants.aspx</t>
         </is>
       </c>
-      <c r="G88" s="11" t="n"/>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Stipend commensurate with qualifications/experience; travel and fringe benefits negotiable</t>
+        </is>
+      </c>
       <c r="H88" s="11" t="n"/>
-      <c r="I88" s="12" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -11517,9 +12996,14 @@
           <t>grad.uci.edu/fellowships/dolores-zohrab-liebmann-fellowship-e</t>
         </is>
       </c>
-      <c r="G89" s="11" t="n"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H89" s="11" t="n"/>
-      <c r="I89" s="12" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -11546,9 +13030,14 @@
           <t>www.loc.gov/programs/john-w-kluge-center/chairs-fellowships/fellowships/larson-fellowship-in-health-and-spirituality</t>
         </is>
       </c>
-      <c r="G90" s="11" t="n"/>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>$5,000/month stipend for up to 12 months</t>
+        </is>
+      </c>
       <c r="H90" s="11" t="n"/>
-      <c r="I90" s="12" t="n"/>
+      <c r="I90" s="11" t="n"/>
+      <c r="J90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -11571,9 +13060,14 @@
           <t>www.pmf.gov</t>
         </is>
       </c>
-      <c r="G91" s="11" t="n"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Federal salary (GS scale) during 2-year fellowship</t>
+        </is>
+      </c>
       <c r="H91" s="11" t="n"/>
-      <c r="I91" s="12" t="n"/>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -11596,9 +13090,14 @@
           <t>www.nsf.gov/honorary-awards/waterman</t>
         </is>
       </c>
-      <c r="G92" s="11" t="n"/>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>$1,000,000 over five years</t>
+        </is>
+      </c>
       <c r="H92" s="11" t="n"/>
-      <c r="I92" s="12" t="n"/>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -11625,9 +13124,14 @@
           <t>www.kccjee.org/graduate-fellowship-program</t>
         </is>
       </c>
-      <c r="G93" s="11" t="n"/>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>$30,000 (one-time)</t>
+        </is>
+      </c>
       <c r="H93" s="11" t="n"/>
-      <c r="I93" s="12" t="n"/>
+      <c r="I93" s="11" t="n"/>
+      <c r="J93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -11654,9 +13158,14 @@
           <t>arg.org/training/postdoctoral-fellowship</t>
         </is>
       </c>
-      <c r="G94" s="11" t="n"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>$64,480-$66,868/year (postdoc) plus benefits</t>
+        </is>
+      </c>
       <c r="H94" s="11" t="n"/>
-      <c r="I94" s="12" t="n"/>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -11683,9 +13192,14 @@
           <t>native-american.dartmouth.edu/research/charles-eastman-fellowship</t>
         </is>
       </c>
-      <c r="G95" s="11" t="n"/>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Not listed: check sponsor page</t>
+        </is>
+      </c>
       <c r="H95" s="11" t="n"/>
-      <c r="I95" s="12" t="n"/>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -11708,9 +13222,14 @@
           <t>www.src.org/program/grc</t>
         </is>
       </c>
-      <c r="G96" s="11" t="n"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>$1,550/month living stipend, tuition and fees for up to 2 years, plus $2,000 annual gift to the student's department</t>
+        </is>
+      </c>
       <c r="H96" s="11" t="n"/>
-      <c r="I96" s="12" t="n"/>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -11737,9 +13256,14 @@
           <t>highways.dot.gov/careers/dwight-david-eisenhower-transportation-fellowship-program</t>
         </is>
       </c>
-      <c r="G97" s="11" t="n"/>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Approx. $1M total available annually across up to ~100 awards</t>
+        </is>
+      </c>
       <c r="H97" s="11" t="n"/>
-      <c r="I97" s="12" t="n"/>
+      <c r="I97" s="11" t="n"/>
+      <c r="J97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -11762,9 +13286,14 @@
           <t>exeter.edu/about/careers/fellowships</t>
         </is>
       </c>
-      <c r="G98" s="11" t="n"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>$23,500 stipend plus up to $3,000 for tuition/health insurance</t>
+        </is>
+      </c>
       <c r="H98" s="11" t="n"/>
-      <c r="I98" s="12" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -11787,19 +13316,24 @@
           <t>www.cnsi.ucsb.edu/programs/elings-fellowships</t>
         </is>
       </c>
-      <c r="G99" s="11" t="n"/>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>$50,000/year salary support plus $2,500/year travel funds, for two years</t>
+        </is>
+      </c>
       <c r="H99" s="11" t="n"/>
-      <c r="I99" s="12" t="n"/>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I99"/>
-  <conditionalFormatting sqref="A2:H99">
+  <autoFilter ref="A1:J99"/>
+  <conditionalFormatting sqref="A2:I99">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$H2&lt;&gt;""</formula>
+      <formula>$I2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Matches,Entered,Sponsor page differs,Record not found"</formula1>
     </dataValidation>
   </dataValidations>
